--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
@@ -469,17 +469,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9776</v>
+        <v>0.9781</v>
       </c>
       <c r="F2" t="n">
-        <v>151.0018</v>
+        <v>148.6799</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>389.328</v>
       </c>
     </row>
     <row r="3">
@@ -498,17 +498,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9799</v>
+        <v>0.9796</v>
       </c>
       <c r="F3" t="n">
-        <v>144.5347</v>
+        <v>145.1952</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>379.1894</v>
       </c>
     </row>
     <row r="4">
@@ -527,17 +527,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9816</v>
+        <v>0.9815</v>
       </c>
       <c r="F4" t="n">
-        <v>147.5769</v>
+        <v>147.9455</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>439.7594</v>
       </c>
     </row>
     <row r="5">
@@ -556,17 +556,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8658</v>
+        <v>0.8661</v>
       </c>
       <c r="F5" t="n">
-        <v>383.2461</v>
+        <v>383.2601</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>644.943</v>
       </c>
     </row>
     <row r="6">
@@ -585,17 +585,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8407</v>
+        <v>0.8495</v>
       </c>
       <c r="F6" t="n">
-        <v>408.4598</v>
+        <v>403.685</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>649.0386999999999</v>
       </c>
     </row>
     <row r="7">
@@ -614,17 +614,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9794</v>
+        <v>0.9789</v>
       </c>
       <c r="F7" t="n">
-        <v>145.8306</v>
+        <v>146.3999</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>404.5824</v>
       </c>
     </row>
     <row r="8">
@@ -643,17 +643,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9749</v>
+        <v>0.9843</v>
       </c>
       <c r="F8" t="n">
-        <v>165.1598</v>
+        <v>133.7186</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>405.1676</v>
       </c>
     </row>
     <row r="9">
@@ -672,17 +672,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9872</v>
+        <v>0.9812</v>
       </c>
       <c r="F9" t="n">
-        <v>123.9127</v>
+        <v>139.1883</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>374.2521</v>
       </c>
     </row>
     <row r="10">
@@ -701,17 +701,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9839</v>
+        <v>0.9843</v>
       </c>
       <c r="F10" t="n">
-        <v>134.7728</v>
+        <v>133.134</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>403.194</v>
       </c>
     </row>
     <row r="11">
@@ -730,17 +730,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9836</v>
+        <v>0.9838</v>
       </c>
       <c r="F11" t="n">
-        <v>135.7184</v>
+        <v>134.671</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>402.6887</v>
       </c>
     </row>
     <row r="12">
@@ -759,17 +759,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.983</v>
+        <v>0.9841</v>
       </c>
       <c r="F12" t="n">
-        <v>139.2297</v>
+        <v>134.2288</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>402.6543</v>
       </c>
     </row>
     <row r="13">
@@ -788,17 +788,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9833</v>
+        <v>0.9836</v>
       </c>
       <c r="F13" t="n">
-        <v>136.8964</v>
+        <v>135.6569</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>404.875</v>
       </c>
     </row>
     <row r="14">
@@ -817,17 +817,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9836</v>
+        <v>0.9839</v>
       </c>
       <c r="F14" t="n">
-        <v>135.6953</v>
+        <v>134.6545</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>402.0988</v>
       </c>
     </row>
     <row r="15">
@@ -846,17 +846,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9839</v>
+        <v>0.9841</v>
       </c>
       <c r="F15" t="n">
-        <v>137.1181</v>
+        <v>134.5873</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>401.3086</v>
       </c>
     </row>
     <row r="16">
@@ -875,17 +875,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9837</v>
+        <v>0.9841</v>
       </c>
       <c r="F16" t="n">
-        <v>136.3045</v>
+        <v>134.9514</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>400.0793</v>
       </c>
     </row>
     <row r="17">
@@ -904,17 +904,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9837</v>
       </c>
       <c r="F17" t="n">
-        <v>136.3711</v>
+        <v>135.197</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>402.6765</v>
       </c>
     </row>
     <row r="18">
@@ -933,17 +933,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9848</v>
+        <v>0.9846</v>
       </c>
       <c r="F18" t="n">
-        <v>128.6995</v>
+        <v>128.6686</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>373.3626</v>
       </c>
     </row>
     <row r="19">
@@ -962,17 +962,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9857</v>
+        <v>0.9785</v>
       </c>
       <c r="F19" t="n">
-        <v>122.9084</v>
+        <v>147.1401</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>371.2747</v>
       </c>
     </row>
     <row r="20">
@@ -991,17 +991,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9839</v>
+        <v>0.9841</v>
       </c>
       <c r="F20" t="n">
-        <v>132.2895</v>
+        <v>132.6741</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>372.652</v>
       </c>
     </row>
     <row r="21">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9849</v>
+        <v>0.9852</v>
       </c>
       <c r="F21" t="n">
-        <v>131.3536</v>
+        <v>128.0559</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>372.561</v>
       </c>
     </row>
     <row r="22">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9855</v>
+        <v>0.9859</v>
       </c>
       <c r="F22" t="n">
-        <v>128.0314</v>
+        <v>127.4023</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>371.1678</v>
       </c>
     </row>
     <row r="23">
@@ -1078,17 +1078,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9847</v>
+        <v>0.9848</v>
       </c>
       <c r="F23" t="n">
-        <v>129.8796</v>
+        <v>129.4109</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>376.9555</v>
       </c>
     </row>
     <row r="24">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9842</v>
+        <v>0.984</v>
       </c>
       <c r="F24" t="n">
-        <v>133.3414</v>
+        <v>133.5638</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>381.4212</v>
       </c>
     </row>
     <row r="25">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9843</v>
+        <v>0.9838</v>
       </c>
       <c r="F25" t="n">
-        <v>132.9595</v>
+        <v>134.1507</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>383.126</v>
       </c>
     </row>
     <row r="26">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9845</v>
+        <v>0.9798</v>
       </c>
       <c r="F26" t="n">
-        <v>127.406</v>
+        <v>145.5075</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>380.4556</v>
       </c>
     </row>
     <row r="27">
@@ -1194,17 +1194,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9852</v>
+        <v>0.9795</v>
       </c>
       <c r="F27" t="n">
-        <v>124.4346</v>
+        <v>143.722</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>370.7932</v>
       </c>
     </row>
     <row r="28">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9805</v>
+        <v>0.9804</v>
       </c>
       <c r="F28" t="n">
-        <v>142.7625</v>
+        <v>142.623</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>370.9471</v>
       </c>
     </row>
     <row r="29">
@@ -1252,17 +1252,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9853</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>128.8933</v>
+        <v>129.2974</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>373.7567</v>
       </c>
     </row>
     <row r="30">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9849</v>
+        <v>0.9852</v>
       </c>
       <c r="F30" t="n">
-        <v>131.4848</v>
+        <v>132.2402</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>373.9786</v>
       </c>
     </row>
     <row r="31">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9771</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>151.8723</v>
+        <v>151.2289</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>370.3915</v>
       </c>
     </row>
     <row r="32">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9855</v>
       </c>
       <c r="F32" t="n">
-        <v>125.3616</v>
+        <v>124.6297</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>371.8649</v>
       </c>
     </row>
     <row r="33">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9845</v>
+        <v>0.9839</v>
       </c>
       <c r="F33" t="n">
-        <v>128.6374</v>
+        <v>129.9522</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>369.45</v>
       </c>
     </row>
     <row r="34">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9686</v>
+        <v>0.9866</v>
       </c>
       <c r="F34" t="n">
-        <v>177.2456</v>
+        <v>121.9888</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>372.0681</v>
       </c>
     </row>
     <row r="35">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9823</v>
+        <v>0.9821</v>
       </c>
       <c r="F35" t="n">
-        <v>137.392</v>
+        <v>138.2053</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>362.577</v>
       </c>
     </row>
     <row r="36">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9857</v>
+        <v>0.9785</v>
       </c>
       <c r="F36" t="n">
-        <v>127.301</v>
+        <v>150.8142</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>377.1881</v>
       </c>
     </row>
     <row r="37">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9792</v>
+        <v>0.9853</v>
       </c>
       <c r="F37" t="n">
-        <v>150.9638</v>
+        <v>127.7184</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>371.2995</v>
       </c>
     </row>
     <row r="38">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.985</v>
+        <v>0.9848</v>
       </c>
       <c r="F38" t="n">
-        <v>124.0744</v>
+        <v>124.868</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>365.1128</v>
       </c>
     </row>
     <row r="39">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9843</v>
       </c>
       <c r="F39" t="n">
-        <v>119.3544</v>
+        <v>123.6423</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>361.2594</v>
       </c>
     </row>
     <row r="40">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9804</v>
+        <v>0.9855</v>
       </c>
       <c r="F40" t="n">
-        <v>142.0318</v>
+        <v>119.4004</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>365.3393</v>
       </c>
     </row>
     <row r="41">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9687</v>
+        <v>0.9816</v>
       </c>
       <c r="F41" t="n">
-        <v>176.7112</v>
+        <v>141.509</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>371.1946</v>
       </c>
     </row>
     <row r="42">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9822</v>
+        <v>0.9819</v>
       </c>
       <c r="F42" t="n">
-        <v>137.8753</v>
+        <v>139.0419</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>362.435</v>
       </c>
     </row>
     <row r="43">
@@ -1658,17 +1658,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9859</v>
+        <v>0.978</v>
       </c>
       <c r="F43" t="n">
-        <v>126.7847</v>
+        <v>151.8265</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>376.1177</v>
       </c>
     </row>
     <row r="44">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9788</v>
+        <v>0.9859</v>
       </c>
       <c r="F44" t="n">
-        <v>152.3987</v>
+        <v>125.7703</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>372.2289</v>
       </c>
     </row>
     <row r="45">
@@ -1716,17 +1716,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9853</v>
+        <v>0.985</v>
       </c>
       <c r="F45" t="n">
-        <v>122.2336</v>
+        <v>123.5471</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>363.58</v>
       </c>
     </row>
     <row r="46">
@@ -1745,17 +1745,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9856</v>
+        <v>0.9846</v>
       </c>
       <c r="F46" t="n">
-        <v>119.9851</v>
+        <v>122.7241</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>361.7853</v>
       </c>
     </row>
     <row r="47">
@@ -1774,17 +1774,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9791</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>142.572</v>
+        <v>120.4483</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>364.1237</v>
       </c>
     </row>
     <row r="48">
@@ -1803,17 +1803,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9833</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>129.7605</v>
+        <v>156.8704</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>387.241</v>
       </c>
     </row>
     <row r="49">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9806</v>
+        <v>0.9875</v>
       </c>
       <c r="F49" t="n">
-        <v>141.8122</v>
+        <v>125.3158</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>375.0064</v>
       </c>
     </row>
     <row r="50">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9091</v>
+        <v>0.8627</v>
       </c>
       <c r="F50" t="n">
-        <v>353.4464</v>
+        <v>401.4208</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>630.4257</v>
       </c>
     </row>
     <row r="51">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8757</v>
       </c>
       <c r="F51" t="n">
-        <v>372.2593</v>
+        <v>391.1494</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>624.3948</v>
       </c>
     </row>
     <row r="52">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E52" t="n">
         <v>0.8816000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>374.4893</v>
+        <v>374.5973</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>621.3458000000001</v>
       </c>
     </row>
     <row r="53">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.8983</v>
+        <v>0.8982</v>
       </c>
       <c r="F53" t="n">
-        <v>370.3972</v>
+        <v>370.5035</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>609.1301</v>
       </c>
     </row>
     <row r="54">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8938</v>
+        <v>0.8939</v>
       </c>
       <c r="F54" t="n">
-        <v>365.5565</v>
+        <v>365.4729</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>598.6323</v>
       </c>
     </row>
     <row r="55">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8572</v>
+        <v>0.8898</v>
       </c>
       <c r="F55" t="n">
-        <v>407.9525</v>
+        <v>372.6439</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>630.5969</v>
       </c>
     </row>
     <row r="56">
@@ -2035,17 +2035,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.872</v>
+        <v>0.8718</v>
       </c>
       <c r="F56" t="n">
-        <v>402.9489</v>
+        <v>403.0006</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>629.2388</v>
       </c>
     </row>
     <row r="57">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
         <v>0.8666</v>
       </c>
       <c r="F57" t="n">
-        <v>399.7331</v>
+        <v>399.7901</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>627.2376</v>
       </c>
     </row>
     <row r="58">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.841</v>
+        <v>0.8485</v>
       </c>
       <c r="F58" t="n">
-        <v>409.2723</v>
+        <v>404.257</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>649.1037</v>
       </c>
     </row>
     <row r="59">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8434</v>
+        <v>0.8448</v>
       </c>
       <c r="F59" t="n">
-        <v>406.7269</v>
+        <v>405.8213</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>647.4867</v>
       </c>
     </row>
     <row r="60">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.845</v>
+        <v>0.8456</v>
       </c>
       <c r="F60" t="n">
-        <v>404.9205</v>
+        <v>404.3935</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>646.873</v>
       </c>
     </row>
     <row r="61">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8655</v>
+        <v>0.8658</v>
       </c>
       <c r="F61" t="n">
-        <v>383.9716</v>
+        <v>384.0545</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>648.3366</v>
       </c>
     </row>
     <row r="62">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
         <v>0.8404</v>
       </c>
       <c r="F62" t="n">
-        <v>415.3734</v>
+        <v>415.3398</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>643.5527</v>
       </c>
     </row>
     <row r="63">
@@ -2238,17 +2238,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8403</v>
+        <v>0.8404</v>
       </c>
       <c r="F63" t="n">
-        <v>413.9531</v>
+        <v>413.7872</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>643.9905</v>
       </c>
     </row>
     <row r="64">
@@ -2267,17 +2267,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8374</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="F64" t="n">
-        <v>415.9947</v>
+        <v>415.9975</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>640.893</v>
       </c>
     </row>
     <row r="65">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>0.8373</v>
       </c>
       <c r="F65" t="n">
-        <v>415.3958</v>
+        <v>415.4063</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>637.9189</v>
       </c>
     </row>
     <row r="66">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8924</v>
+        <v>0.8925</v>
       </c>
       <c r="F66" t="n">
-        <v>366.0203</v>
+        <v>365.9201</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>625.7428</v>
       </c>
     </row>
     <row r="67">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9022</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>357.861</v>
+        <v>357.9847</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>626.057</v>
       </c>
     </row>
     <row r="68">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.8602</v>
       </c>
       <c r="F68" t="n">
-        <v>404.6496</v>
+        <v>404.8312</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>628.9651</v>
       </c>
     </row>
     <row r="69">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9837</v>
       </c>
       <c r="F69" t="n">
-        <v>133.4046</v>
+        <v>132.2083</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>371.5164</v>
       </c>
     </row>
     <row r="70">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E70" t="n">
         <v>0.9849</v>
       </c>
       <c r="F70" t="n">
-        <v>129.6025</v>
+        <v>129.831</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>367.0531</v>
       </c>
     </row>
     <row r="71">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9764</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>154.0113</v>
+        <v>154.2362</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>382.3624</v>
       </c>
     </row>
     <row r="72">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9839</v>
+        <v>0.9846</v>
       </c>
       <c r="F72" t="n">
-        <v>131.055</v>
+        <v>128.6414</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>374.5832</v>
       </c>
     </row>
     <row r="73">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9754</v>
+        <v>0.9534</v>
       </c>
       <c r="F73" t="n">
-        <v>165.5939</v>
+        <v>217.8375</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>393.5632</v>
       </c>
     </row>
     <row r="74">
@@ -2557,17 +2557,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E74" t="n">
         <v>0.9608</v>
       </c>
       <c r="F74" t="n">
-        <v>195.4857</v>
+        <v>195.7516</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>389.167</v>
       </c>
     </row>
     <row r="75">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E75" t="n">
         <v>0.9813</v>
       </c>
       <c r="F75" t="n">
-        <v>142.5927</v>
+        <v>142.3639</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>421.2</v>
       </c>
     </row>
     <row r="76">
@@ -2615,17 +2615,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>0.9813</v>
       </c>
       <c r="F76" t="n">
-        <v>142.5927</v>
+        <v>142.3639</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>421.2</v>
       </c>
     </row>
     <row r="77">
@@ -2644,17 +2644,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>0.8078</v>
       </c>
       <c r="F77" t="n">
-        <v>436.3437</v>
+        <v>436.2959</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>645.96</v>
       </c>
     </row>
     <row r="78">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8081</v>
+        <v>0.8083</v>
       </c>
       <c r="F78" t="n">
-        <v>436.3421</v>
+        <v>436.2032</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>645.3871</v>
       </c>
     </row>
     <row r="79">
@@ -2702,17 +2702,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8054</v>
+        <v>0.8056</v>
       </c>
       <c r="F79" t="n">
-        <v>437.1674</v>
+        <v>437.057</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>646.0196</v>
       </c>
     </row>
     <row r="80">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8082</v>
+        <v>0.8083</v>
       </c>
       <c r="F80" t="n">
-        <v>436.4915</v>
+        <v>436.3704</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>645.3563</v>
       </c>
     </row>
     <row r="81">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.879</v>
+        <v>0.8786</v>
       </c>
       <c r="F81" t="n">
-        <v>377.9655</v>
+        <v>378.13</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>630.4403</v>
       </c>
     </row>
     <row r="82">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E82" t="n">
         <v>0.8505</v>
       </c>
       <c r="F82" t="n">
-        <v>407.6927</v>
+        <v>407.7278</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>634.6656</v>
       </c>
     </row>
     <row r="83">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9809</v>
+        <v>0.9808</v>
       </c>
       <c r="F83" t="n">
-        <v>143.2605</v>
+        <v>143.341</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>424.2604</v>
       </c>
     </row>
     <row r="84">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9809</v>
+        <v>0.9807</v>
       </c>
       <c r="F84" t="n">
-        <v>143.3128</v>
+        <v>143.6662</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>423.838</v>
       </c>
     </row>
     <row r="85">
@@ -2876,17 +2876,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.981</v>
+        <v>0.9809</v>
       </c>
       <c r="F85" t="n">
-        <v>143.1284</v>
+        <v>143.2959</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>425.1692</v>
       </c>
     </row>
     <row r="86">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9784</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="F86" t="n">
-        <v>151.3505</v>
+        <v>147.9625</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>386.1339</v>
       </c>
     </row>
     <row r="87">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9781</v>
+        <v>0.9856</v>
       </c>
       <c r="F87" t="n">
-        <v>149.6426</v>
+        <v>129.8917</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>384.5359</v>
       </c>
     </row>
     <row r="88">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.985</v>
+        <v>0.9848</v>
       </c>
       <c r="F88" t="n">
-        <v>131.871</v>
+        <v>133.1557</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>386.1375</v>
       </c>
     </row>
     <row r="89">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9764</v>
+        <v>0.9765</v>
       </c>
       <c r="F89" t="n">
-        <v>155.2124</v>
+        <v>155.3333</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>390.7489</v>
       </c>
     </row>
     <row r="90">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9859</v>
+        <v>0.978</v>
       </c>
       <c r="F90" t="n">
-        <v>126.6016</v>
+        <v>151.8241</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>376.4453</v>
       </c>
     </row>
     <row r="91">
@@ -3050,17 +3050,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9788</v>
+        <v>0.9859</v>
       </c>
       <c r="F91" t="n">
-        <v>152.3987</v>
+        <v>125.7703</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>371.8546</v>
       </c>
     </row>
     <row r="92">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.985</v>
+        <v>0.9848</v>
       </c>
       <c r="F92" t="n">
-        <v>131.871</v>
+        <v>133.1557</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>386.1375</v>
       </c>
     </row>
     <row r="93">
@@ -3108,17 +3108,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9788</v>
+        <v>0.9859</v>
       </c>
       <c r="F93" t="n">
-        <v>152.3987</v>
+        <v>125.7703</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>371.8546</v>
       </c>
     </row>
     <row r="94">
@@ -3137,17 +3137,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9816</v>
+        <v>0.9815</v>
       </c>
       <c r="F94" t="n">
-        <v>147.5769</v>
+        <v>147.9455</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>439.7594</v>
       </c>
     </row>
     <row r="95">
@@ -3166,17 +3166,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.7973</v>
+        <v>0.7975</v>
       </c>
       <c r="F95" t="n">
-        <v>473.3602</v>
+        <v>473.2703</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>710.3605</v>
       </c>
     </row>
     <row r="96">
@@ -3195,17 +3195,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E96" t="n">
         <v>0.9818</v>
       </c>
       <c r="F96" t="n">
-        <v>146.8033</v>
+        <v>147.0156</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>439.2864</v>
       </c>
     </row>
     <row r="97">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E97" t="n">
         <v>0.9819</v>
       </c>
       <c r="F97" t="n">
-        <v>146.3482</v>
+        <v>146.5793</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>439.5177</v>
       </c>
     </row>
     <row r="98">
@@ -3253,17 +3253,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E98" t="n">
         <v>0.986</v>
       </c>
       <c r="F98" t="n">
-        <v>130.6951</v>
+        <v>130.6339</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>373.0217</v>
       </c>
     </row>
     <row r="99">
@@ -3282,17 +3282,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9861</v>
+        <v>0.9847</v>
       </c>
       <c r="F99" t="n">
-        <v>128.69</v>
+        <v>133.2663</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>372.1863</v>
       </c>
     </row>
     <row r="100">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E100" t="n">
         <v>0.9856</v>
       </c>
       <c r="F100" t="n">
-        <v>129.6253</v>
+        <v>130.7212</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>375.2522</v>
       </c>
     </row>
     <row r="101">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9853</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="F101" t="n">
-        <v>129.7998</v>
+        <v>129.8188</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>376.4327</v>
       </c>
     </row>
     <row r="102">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E102" t="n">
         <v>0.9857</v>
       </c>
       <c r="F102" t="n">
-        <v>129.0183</v>
+        <v>128.3649</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>381.785</v>
       </c>
     </row>
     <row r="103">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E103" t="n">
         <v>0.9864000000000001</v>
       </c>
       <c r="F103" t="n">
-        <v>130.4808</v>
+        <v>129.5243</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>377.6631</v>
       </c>
     </row>
     <row r="104">
@@ -3427,17 +3427,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9862</v>
+        <v>0.9861</v>
       </c>
       <c r="F104" t="n">
-        <v>129.0636</v>
+        <v>128.943</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>374.9032</v>
       </c>
     </row>
     <row r="105">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9801</v>
+        <v>0.98</v>
       </c>
       <c r="F105" t="n">
-        <v>148.7509</v>
+        <v>149.144</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>373.1885</v>
       </c>
     </row>
     <row r="106">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9839</v>
+        <v>0.9842</v>
       </c>
       <c r="F106" t="n">
-        <v>134.3619</v>
+        <v>133.8707</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>369.8204</v>
       </c>
     </row>
     <row r="107">
@@ -3514,17 +3514,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E107" t="n">
         <v>0.9852</v>
       </c>
       <c r="F107" t="n">
-        <v>130.4333</v>
+        <v>130.7216</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>375.8617</v>
       </c>
     </row>
     <row r="108">
@@ -3543,17 +3543,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.985</v>
+        <v>0.9857</v>
       </c>
       <c r="F108" t="n">
-        <v>138.4288</v>
+        <v>138.0156</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>402.4533</v>
       </c>
     </row>
     <row r="109">
@@ -3572,17 +3572,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9837</v>
+        <v>0.982</v>
       </c>
       <c r="F109" t="n">
-        <v>143.3367</v>
+        <v>146.728</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>374.4102</v>
       </c>
     </row>
     <row r="110">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9845</v>
+        <v>0.9848</v>
       </c>
       <c r="F110" t="n">
-        <v>131.4774</v>
+        <v>130.263</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>375.9279</v>
       </c>
     </row>
     <row r="111">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9778</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F111" t="n">
-        <v>154.6854</v>
+        <v>153.3862</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>375.2357</v>
       </c>
     </row>
     <row r="112">
@@ -3659,17 +3659,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9858</v>
       </c>
       <c r="F112" t="n">
-        <v>136.5913</v>
+        <v>135.8231</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>399.7492</v>
       </c>
     </row>
     <row r="113">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.982</v>
+        <v>0.9822</v>
       </c>
       <c r="F113" t="n">
-        <v>147.1039</v>
+        <v>146.349</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>373.6126</v>
       </c>
     </row>
     <row r="114">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9846</v>
+        <v>0.9836</v>
       </c>
       <c r="F114" t="n">
-        <v>130.7906</v>
+        <v>134.7114</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>373.8665</v>
       </c>
     </row>
     <row r="115">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9775</v>
+        <v>0.978</v>
       </c>
       <c r="F115" t="n">
-        <v>155.5376</v>
+        <v>154.1862</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>375.3984</v>
       </c>
     </row>
     <row r="116">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.8847</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="F116" t="n">
-        <v>365.6212</v>
+        <v>364.9176</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>641.3001</v>
       </c>
     </row>
     <row r="117">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8756</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="F117" t="n">
-        <v>371.8688</v>
+        <v>371.1572</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>644.6944999999999</v>
       </c>
     </row>
     <row r="118">
@@ -3833,17 +3833,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9801</v>
+        <v>0.98</v>
       </c>
       <c r="F118" t="n">
-        <v>148.7509</v>
+        <v>149.144</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>373.1885</v>
       </c>
     </row>
     <row r="119">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.982</v>
+        <v>0.9822</v>
       </c>
       <c r="F119" t="n">
-        <v>147.1039</v>
+        <v>146.349</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>373.6126</v>
       </c>
     </row>
     <row r="120">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.969</v>
+        <v>0.9363</v>
       </c>
       <c r="F120" t="n">
-        <v>175.3093</v>
+        <v>239.9007</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>390.8713</v>
       </c>
     </row>
     <row r="121">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.969</v>
+        <v>0.9363</v>
       </c>
       <c r="F121" t="n">
-        <v>175.3093</v>
+        <v>239.9007</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>390.8713</v>
       </c>
     </row>
     <row r="122">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9748</v>
+        <v>0.9744</v>
       </c>
       <c r="F122" t="n">
-        <v>154.2597</v>
+        <v>155.3144</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>355.3553</v>
       </c>
     </row>
     <row r="123">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9861</v>
+        <v>0.9821</v>
       </c>
       <c r="F123" t="n">
-        <v>132.219</v>
+        <v>146.8122</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>373.5886</v>
       </c>
     </row>
     <row r="124">
@@ -4007,17 +4007,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9782</v>
+        <v>0.9781</v>
       </c>
       <c r="F124" t="n">
-        <v>159.3939</v>
+        <v>159.782</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>381.1461</v>
       </c>
     </row>
     <row r="125">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9663</v>
+        <v>0.9812</v>
       </c>
       <c r="F125" t="n">
-        <v>189.7065</v>
+        <v>148.5925</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>441.527</v>
       </c>
     </row>
     <row r="126">
@@ -4065,17 +4065,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9805</v>
+        <v>0.9801</v>
       </c>
       <c r="F126" t="n">
-        <v>143.7397</v>
+        <v>145.2877</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>377.7509</v>
       </c>
     </row>
     <row r="127">
@@ -4094,17 +4094,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.8445</v>
+        <v>0.8449</v>
       </c>
       <c r="F127" t="n">
-        <v>411.0666</v>
+        <v>411.4272</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>670.217</v>
       </c>
     </row>
     <row r="128">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.9855</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="F128" t="n">
-        <v>129.4862</v>
+        <v>130.3922</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>386.1908</v>
       </c>
     </row>
     <row r="129">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.9856</v>
+        <v>0.9858</v>
       </c>
       <c r="F129" t="n">
-        <v>128.8912</v>
+        <v>129.2235</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>385.9443</v>
       </c>
     </row>
     <row r="130">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.9856</v>
+        <v>0.985</v>
       </c>
       <c r="F130" t="n">
-        <v>128.9549</v>
+        <v>129.3455</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>385.7534</v>
       </c>
     </row>
     <row r="131">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9779</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>155.306</v>
+        <v>129.8148</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>388.8385</v>
       </c>
     </row>
     <row r="132">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.9853</v>
+        <v>0.9794</v>
       </c>
       <c r="F132" t="n">
-        <v>124.5626</v>
+        <v>147.1833</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>382.8252</v>
       </c>
     </row>
     <row r="133">
@@ -4268,17 +4268,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9794</v>
+        <v>0.9789</v>
       </c>
       <c r="F133" t="n">
-        <v>147.2106</v>
+        <v>148.5293</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>383.0337</v>
       </c>
     </row>
     <row r="134">
@@ -4297,17 +4297,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9785</v>
+        <v>0.9784</v>
       </c>
       <c r="F134" t="n">
-        <v>149.5552</v>
+        <v>150.0476</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>383.519</v>
       </c>
     </row>
     <row r="135">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E135" t="n">
         <v>0.9858</v>
       </c>
       <c r="F135" t="n">
-        <v>128.6437</v>
+        <v>129.0591</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>385.4843</v>
       </c>
     </row>
     <row r="136">
@@ -4355,17 +4355,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.9856</v>
+        <v>0.9857</v>
       </c>
       <c r="F136" t="n">
-        <v>128.7184</v>
+        <v>128.563</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>387.002</v>
       </c>
     </row>
     <row r="137">
@@ -4384,17 +4384,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9805</v>
+        <v>0.9807</v>
       </c>
       <c r="F137" t="n">
-        <v>142.6515</v>
+        <v>141.863</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>371.2664</v>
       </c>
     </row>
     <row r="138">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9835</v>
+        <v>0.9759</v>
       </c>
       <c r="F138" t="n">
-        <v>130.2547</v>
+        <v>156.4093</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>371.2769</v>
       </c>
     </row>
     <row r="139">
@@ -4442,17 +4442,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9846</v>
+        <v>0.9805</v>
       </c>
       <c r="F139" t="n">
-        <v>127.7084</v>
+        <v>142.4346</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>371.3006</v>
       </c>
     </row>
     <row r="140">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E140" t="n">
         <v>0.9852</v>
       </c>
       <c r="F140" t="n">
-        <v>128.8108</v>
+        <v>129.0378</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>363.254</v>
       </c>
     </row>
     <row r="141">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9856</v>
+        <v>0.9857</v>
       </c>
       <c r="F141" t="n">
-        <v>126.6262</v>
+        <v>127.3827</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>360.3129</v>
       </c>
     </row>
     <row r="142">
@@ -4529,17 +4529,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9835</v>
+        <v>0.9759</v>
       </c>
       <c r="F142" t="n">
-        <v>130.2547</v>
+        <v>156.4093</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>371.2769</v>
       </c>
     </row>
     <row r="143">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.98</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F143" t="n">
-        <v>142.905</v>
+        <v>149.5814</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>370.9851</v>
       </c>
     </row>
     <row r="144">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9789</v>
+        <v>0.9791</v>
       </c>
       <c r="F144" t="n">
-        <v>145.383</v>
+        <v>144.9349</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>368.6119</v>
       </c>
     </row>
     <row r="145">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9856</v>
+        <v>0.9857</v>
       </c>
       <c r="F145" t="n">
-        <v>126.6262</v>
+        <v>127.3827</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>360.3129</v>
       </c>
     </row>
     <row r="146">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.8472</v>
+        <v>0.8467</v>
       </c>
       <c r="F146" t="n">
-        <v>411.2704</v>
+        <v>412.102</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>666.9450000000001</v>
       </c>
     </row>
     <row r="147">
@@ -4674,17 +4674,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.8485</v>
+        <v>0.8487</v>
       </c>
       <c r="F147" t="n">
-        <v>409.1429</v>
+        <v>409.4122</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>668.597</v>
       </c>
     </row>
     <row r="148">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.8446</v>
+        <v>0.8445</v>
       </c>
       <c r="F148" t="n">
-        <v>413.317</v>
+        <v>413.5223</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>668.5302</v>
       </c>
     </row>
     <row r="149">
@@ -4732,17 +4732,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.844</v>
+        <v>0.8437</v>
       </c>
       <c r="F149" t="n">
-        <v>413.6729</v>
+        <v>413.7097</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>669.2008</v>
       </c>
     </row>
     <row r="150">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.8456</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="F150" t="n">
-        <v>410.4531</v>
+        <v>410.2758</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>668.3015</v>
       </c>
     </row>
     <row r="151">
@@ -4790,17 +4790,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.8467</v>
       </c>
       <c r="F151" t="n">
-        <v>409.5182</v>
+        <v>409.413</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>669.2895</v>
       </c>
     </row>
     <row r="152">
@@ -4819,17 +4819,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.8468</v>
       </c>
       <c r="F152" t="n">
-        <v>410.6881</v>
+        <v>410.5961</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>669.7025</v>
       </c>
     </row>
     <row r="153">
@@ -4848,17 +4848,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.8435</v>
       </c>
       <c r="F153" t="n">
-        <v>413.4273</v>
+        <v>413.7241</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>668.6964</v>
       </c>
     </row>
     <row r="154">
@@ -4877,17 +4877,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.8455</v>
+        <v>0.8468</v>
       </c>
       <c r="F154" t="n">
-        <v>412.7821</v>
+        <v>411.9744</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>668.6466</v>
       </c>
     </row>
     <row r="155">
@@ -4906,17 +4906,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.8824</v>
+        <v>0.8822</v>
       </c>
       <c r="F155" t="n">
-        <v>382.1607</v>
+        <v>382.0004</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>636.3786</v>
       </c>
     </row>
     <row r="156">
@@ -4935,17 +4935,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E156" t="n">
         <v>0.844</v>
       </c>
       <c r="F156" t="n">
-        <v>415.3096</v>
+        <v>415.492</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>643.5905</v>
       </c>
     </row>
     <row r="157">
@@ -4964,17 +4964,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.8618</v>
+        <v>0.8617</v>
       </c>
       <c r="F157" t="n">
-        <v>399.053</v>
+        <v>399.1334</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>640.7482</v>
       </c>
     </row>
     <row r="158">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.8572</v>
+        <v>0.8575</v>
       </c>
       <c r="F158" t="n">
-        <v>410.3622</v>
+        <v>410.2638</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>627.1333</v>
       </c>
     </row>
     <row r="159">
@@ -5022,17 +5022,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.9853</v>
+        <v>0.9786</v>
       </c>
       <c r="F159" t="n">
-        <v>124.0843</v>
+        <v>145.9842</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>362.0362</v>
       </c>
     </row>
     <row r="160">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.8079</v>
+        <v>0.8078</v>
       </c>
       <c r="F160" t="n">
-        <v>449.5804</v>
+        <v>449.6392</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>664.2560999999999</v>
       </c>
     </row>
     <row r="161">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.8456</v>
+        <v>0.8455</v>
       </c>
       <c r="F161" t="n">
-        <v>414.116</v>
+        <v>414.278</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>664.4628</v>
       </c>
     </row>
     <row r="162">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9781</v>
+        <v>0.978</v>
       </c>
       <c r="F162" t="n">
-        <v>147.8347</v>
+        <v>148.4737</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>368.2855</v>
       </c>
     </row>
     <row r="163">
@@ -5138,17 +5138,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9852</v>
+        <v>0.9845</v>
       </c>
       <c r="F163" t="n">
-        <v>125.8638</v>
+        <v>129.1146</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>377.2004</v>
       </c>
     </row>
     <row r="164">
@@ -5167,17 +5167,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9853</v>
+        <v>0.9852</v>
       </c>
       <c r="F164" t="n">
-        <v>129.016</v>
+        <v>129.1936</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>364.0913</v>
       </c>
     </row>
     <row r="165">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9663</v>
+        <v>0.9812</v>
       </c>
       <c r="F165" t="n">
-        <v>189.7065</v>
+        <v>148.5925</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>441.527</v>
       </c>
     </row>
     <row r="166">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E166" t="n">
         <v>0.7924</v>
       </c>
       <c r="F166" t="n">
-        <v>474.0989</v>
+        <v>474.0217</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>710.4115</v>
       </c>
     </row>
     <row r="167">
@@ -5254,17 +5254,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9781</v>
       </c>
       <c r="F167" t="n">
-        <v>150.9474</v>
+        <v>151.5051</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>359.715</v>
       </c>
     </row>
     <row r="168">
@@ -5283,17 +5283,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.986</v>
       </c>
       <c r="F168" t="n">
-        <v>123.799</v>
+        <v>125.1871</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>349.9414</v>
       </c>
     </row>
     <row r="169">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9751</v>
+        <v>0.9752</v>
       </c>
       <c r="F169" t="n">
-        <v>158.7886</v>
+        <v>158.9385</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>388.1476</v>
       </c>
     </row>
     <row r="170">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9843</v>
+        <v>0.9839</v>
       </c>
       <c r="F170" t="n">
-        <v>136.8282</v>
+        <v>137.8683</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>402.3166</v>
       </c>
     </row>
     <row r="171">
@@ -5370,17 +5370,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9774</v>
+        <v>0.9772</v>
       </c>
       <c r="F171" t="n">
-        <v>156.7173</v>
+        <v>156.5498</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>369.4755</v>
       </c>
     </row>
     <row r="172">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9798</v>
+        <v>0.98</v>
       </c>
       <c r="F172" t="n">
-        <v>144.5319</v>
+        <v>143.5005</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>362.3605</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,10 +444,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>RMSEC</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>RMSECV</t>
         </is>
@@ -476,9 +481,12 @@
         <v>0.9781</v>
       </c>
       <c r="F2" t="n">
+        <v>1.3444</v>
+      </c>
+      <c r="G2" t="n">
         <v>148.6799</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>389.328</v>
       </c>
     </row>
@@ -505,9 +513,12 @@
         <v>0.9796</v>
       </c>
       <c r="F3" t="n">
+        <v>1.3267</v>
+      </c>
+      <c r="G3" t="n">
         <v>145.1952</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>379.1894</v>
       </c>
     </row>
@@ -534,9 +545,12 @@
         <v>0.9815</v>
       </c>
       <c r="F4" t="n">
+        <v>1.4394</v>
+      </c>
+      <c r="G4" t="n">
         <v>147.9455</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>439.7594</v>
       </c>
     </row>
@@ -563,9 +577,12 @@
         <v>0.8661</v>
       </c>
       <c r="F5" t="n">
+        <v>1.9451</v>
+      </c>
+      <c r="G5" t="n">
         <v>383.2601</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>644.943</v>
       </c>
     </row>
@@ -592,9 +609,12 @@
         <v>0.8495</v>
       </c>
       <c r="F6" t="n">
+        <v>1.9572</v>
+      </c>
+      <c r="G6" t="n">
         <v>403.685</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>649.0386999999999</v>
       </c>
     </row>
@@ -621,9 +641,12 @@
         <v>0.9789</v>
       </c>
       <c r="F7" t="n">
+        <v>1.3719</v>
+      </c>
+      <c r="G7" t="n">
         <v>146.3999</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>404.5824</v>
       </c>
     </row>
@@ -650,9 +673,12 @@
         <v>0.9843</v>
       </c>
       <c r="F8" t="n">
+        <v>1.373</v>
+      </c>
+      <c r="G8" t="n">
         <v>133.7186</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>405.1676</v>
       </c>
     </row>
@@ -679,9 +705,12 @@
         <v>0.9812</v>
       </c>
       <c r="F9" t="n">
+        <v>1.3183</v>
+      </c>
+      <c r="G9" t="n">
         <v>139.1883</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>374.2521</v>
       </c>
     </row>
@@ -708,9 +737,12 @@
         <v>0.9843</v>
       </c>
       <c r="F10" t="n">
+        <v>1.3694</v>
+      </c>
+      <c r="G10" t="n">
         <v>133.134</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>403.194</v>
       </c>
     </row>
@@ -737,9 +769,12 @@
         <v>0.9838</v>
       </c>
       <c r="F11" t="n">
+        <v>1.3685</v>
+      </c>
+      <c r="G11" t="n">
         <v>134.671</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>402.6887</v>
       </c>
     </row>
@@ -766,9 +801,12 @@
         <v>0.9841</v>
       </c>
       <c r="F12" t="n">
+        <v>1.3684</v>
+      </c>
+      <c r="G12" t="n">
         <v>134.2288</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>402.6543</v>
       </c>
     </row>
@@ -795,9 +833,12 @@
         <v>0.9836</v>
       </c>
       <c r="F13" t="n">
+        <v>1.3725</v>
+      </c>
+      <c r="G13" t="n">
         <v>135.6569</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>404.875</v>
       </c>
     </row>
@@ -824,9 +865,12 @@
         <v>0.9839</v>
       </c>
       <c r="F14" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="G14" t="n">
         <v>134.6545</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>402.0988</v>
       </c>
     </row>
@@ -853,9 +897,12 @@
         <v>0.9841</v>
       </c>
       <c r="F15" t="n">
+        <v>1.3659</v>
+      </c>
+      <c r="G15" t="n">
         <v>134.5873</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>401.3086</v>
       </c>
     </row>
@@ -882,9 +929,12 @@
         <v>0.9841</v>
       </c>
       <c r="F16" t="n">
+        <v>1.3637</v>
+      </c>
+      <c r="G16" t="n">
         <v>134.9514</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>400.0793</v>
       </c>
     </row>
@@ -911,9 +961,12 @@
         <v>0.9837</v>
       </c>
       <c r="F17" t="n">
+        <v>1.3684</v>
+      </c>
+      <c r="G17" t="n">
         <v>135.197</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>402.6765</v>
       </c>
     </row>
@@ -940,9 +993,12 @@
         <v>0.9846</v>
       </c>
       <c r="F18" t="n">
+        <v>1.3168</v>
+      </c>
+      <c r="G18" t="n">
         <v>128.6686</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>373.3626</v>
       </c>
     </row>
@@ -969,9 +1025,12 @@
         <v>0.9785</v>
       </c>
       <c r="F19" t="n">
+        <v>1.3132</v>
+      </c>
+      <c r="G19" t="n">
         <v>147.1401</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>371.2747</v>
       </c>
     </row>
@@ -998,9 +1057,12 @@
         <v>0.9841</v>
       </c>
       <c r="F20" t="n">
+        <v>1.3155</v>
+      </c>
+      <c r="G20" t="n">
         <v>132.6741</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>372.652</v>
       </c>
     </row>
@@ -1027,9 +1089,12 @@
         <v>0.9852</v>
       </c>
       <c r="F21" t="n">
+        <v>1.3154</v>
+      </c>
+      <c r="G21" t="n">
         <v>128.0559</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>372.561</v>
       </c>
     </row>
@@ -1056,9 +1121,12 @@
         <v>0.9859</v>
       </c>
       <c r="F22" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="G22" t="n">
         <v>127.4023</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>371.1678</v>
       </c>
     </row>
@@ -1085,9 +1153,12 @@
         <v>0.9848</v>
       </c>
       <c r="F23" t="n">
+        <v>1.3229</v>
+      </c>
+      <c r="G23" t="n">
         <v>129.4109</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>376.9555</v>
       </c>
     </row>
@@ -1114,9 +1185,12 @@
         <v>0.984</v>
       </c>
       <c r="F24" t="n">
+        <v>1.3306</v>
+      </c>
+      <c r="G24" t="n">
         <v>133.5638</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>381.4212</v>
       </c>
     </row>
@@ -1143,9 +1217,12 @@
         <v>0.9838</v>
       </c>
       <c r="F25" t="n">
+        <v>1.3335</v>
+      </c>
+      <c r="G25" t="n">
         <v>134.1507</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>383.126</v>
       </c>
     </row>
@@ -1172,9 +1249,12 @@
         <v>0.9798</v>
       </c>
       <c r="F26" t="n">
+        <v>1.3289</v>
+      </c>
+      <c r="G26" t="n">
         <v>145.5075</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>380.4556</v>
       </c>
     </row>
@@ -1201,9 +1281,12 @@
         <v>0.9795</v>
       </c>
       <c r="F27" t="n">
+        <v>1.3124</v>
+      </c>
+      <c r="G27" t="n">
         <v>143.722</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>370.7932</v>
       </c>
     </row>
@@ -1230,9 +1313,12 @@
         <v>0.9804</v>
       </c>
       <c r="F28" t="n">
+        <v>1.3127</v>
+      </c>
+      <c r="G28" t="n">
         <v>142.623</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>370.9471</v>
       </c>
     </row>
@@ -1259,9 +1345,12 @@
         <v>0.9854000000000001</v>
       </c>
       <c r="F29" t="n">
+        <v>1.3174</v>
+      </c>
+      <c r="G29" t="n">
         <v>129.2974</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>373.7567</v>
       </c>
     </row>
@@ -1288,9 +1377,12 @@
         <v>0.9852</v>
       </c>
       <c r="F30" t="n">
+        <v>1.3178</v>
+      </c>
+      <c r="G30" t="n">
         <v>132.2402</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>373.9786</v>
       </c>
     </row>
@@ -1317,9 +1409,12 @@
         <v>0.9772999999999999</v>
       </c>
       <c r="F31" t="n">
+        <v>1.3117</v>
+      </c>
+      <c r="G31" t="n">
         <v>151.2289</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>370.3915</v>
       </c>
     </row>
@@ -1346,9 +1441,12 @@
         <v>0.9855</v>
       </c>
       <c r="F32" t="n">
+        <v>1.3142</v>
+      </c>
+      <c r="G32" t="n">
         <v>124.6297</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>371.8649</v>
       </c>
     </row>
@@ -1375,9 +1473,12 @@
         <v>0.9839</v>
       </c>
       <c r="F33" t="n">
+        <v>1.3101</v>
+      </c>
+      <c r="G33" t="n">
         <v>129.9522</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>369.45</v>
       </c>
     </row>
@@ -1404,9 +1505,12 @@
         <v>0.9866</v>
       </c>
       <c r="F34" t="n">
+        <v>1.3146</v>
+      </c>
+      <c r="G34" t="n">
         <v>121.9888</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>372.0681</v>
       </c>
     </row>
@@ -1433,9 +1537,12 @@
         <v>0.9821</v>
       </c>
       <c r="F35" t="n">
+        <v>1.2987</v>
+      </c>
+      <c r="G35" t="n">
         <v>138.2053</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>362.577</v>
       </c>
     </row>
@@ -1462,9 +1569,12 @@
         <v>0.9785</v>
       </c>
       <c r="F36" t="n">
+        <v>1.3233</v>
+      </c>
+      <c r="G36" t="n">
         <v>150.8142</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>377.1881</v>
       </c>
     </row>
@@ -1491,9 +1601,12 @@
         <v>0.9853</v>
       </c>
       <c r="F37" t="n">
+        <v>1.3133</v>
+      </c>
+      <c r="G37" t="n">
         <v>127.7184</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>371.2995</v>
       </c>
     </row>
@@ -1520,9 +1633,12 @@
         <v>0.9848</v>
       </c>
       <c r="F38" t="n">
+        <v>1.3029</v>
+      </c>
+      <c r="G38" t="n">
         <v>124.868</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>365.1128</v>
       </c>
     </row>
@@ -1549,9 +1665,12 @@
         <v>0.9843</v>
       </c>
       <c r="F39" t="n">
+        <v>1.2965</v>
+      </c>
+      <c r="G39" t="n">
         <v>123.6423</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>361.2594</v>
       </c>
     </row>
@@ -1578,9 +1697,12 @@
         <v>0.9855</v>
       </c>
       <c r="F40" t="n">
+        <v>1.3033</v>
+      </c>
+      <c r="G40" t="n">
         <v>119.4004</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>365.3393</v>
       </c>
     </row>
@@ -1607,9 +1729,12 @@
         <v>0.9816</v>
       </c>
       <c r="F41" t="n">
+        <v>1.3131</v>
+      </c>
+      <c r="G41" t="n">
         <v>141.509</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>371.1946</v>
       </c>
     </row>
@@ -1636,9 +1761,12 @@
         <v>0.9819</v>
       </c>
       <c r="F42" t="n">
+        <v>1.2985</v>
+      </c>
+      <c r="G42" t="n">
         <v>139.0419</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>362.435</v>
       </c>
     </row>
@@ -1665,9 +1793,12 @@
         <v>0.978</v>
       </c>
       <c r="F43" t="n">
+        <v>1.3214</v>
+      </c>
+      <c r="G43" t="n">
         <v>151.8265</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>376.1177</v>
       </c>
     </row>
@@ -1694,9 +1825,12 @@
         <v>0.9859</v>
       </c>
       <c r="F44" t="n">
+        <v>1.3148</v>
+      </c>
+      <c r="G44" t="n">
         <v>125.7703</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>372.2289</v>
       </c>
     </row>
@@ -1723,9 +1857,12 @@
         <v>0.985</v>
       </c>
       <c r="F45" t="n">
+        <v>1.3004</v>
+      </c>
+      <c r="G45" t="n">
         <v>123.5471</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>363.58</v>
       </c>
     </row>
@@ -1752,9 +1889,12 @@
         <v>0.9846</v>
       </c>
       <c r="F46" t="n">
+        <v>1.2974</v>
+      </c>
+      <c r="G46" t="n">
         <v>122.7241</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>361.7853</v>
       </c>
     </row>
@@ -1781,9 +1921,12 @@
         <v>0.9854000000000001</v>
       </c>
       <c r="F47" t="n">
+        <v>1.3013</v>
+      </c>
+      <c r="G47" t="n">
         <v>120.4483</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>364.1237</v>
       </c>
     </row>
@@ -1810,9 +1953,12 @@
         <v>0.9782999999999999</v>
       </c>
       <c r="F48" t="n">
+        <v>1.3407</v>
+      </c>
+      <c r="G48" t="n">
         <v>156.8704</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>387.241</v>
       </c>
     </row>
@@ -1839,9 +1985,12 @@
         <v>0.9875</v>
       </c>
       <c r="F49" t="n">
+        <v>1.3195</v>
+      </c>
+      <c r="G49" t="n">
         <v>125.3158</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>375.0064</v>
       </c>
     </row>
@@ -1868,9 +2017,12 @@
         <v>0.8627</v>
       </c>
       <c r="F50" t="n">
+        <v>1.9031</v>
+      </c>
+      <c r="G50" t="n">
         <v>401.4208</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>630.4257</v>
       </c>
     </row>
@@ -1897,9 +2049,12 @@
         <v>0.8757</v>
       </c>
       <c r="F51" t="n">
+        <v>1.8859</v>
+      </c>
+      <c r="G51" t="n">
         <v>391.1494</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>624.3948</v>
       </c>
     </row>
@@ -1926,9 +2081,12 @@
         <v>0.8816000000000001</v>
       </c>
       <c r="F52" t="n">
+        <v>1.8772</v>
+      </c>
+      <c r="G52" t="n">
         <v>374.5973</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>621.3458000000001</v>
       </c>
     </row>
@@ -1955,9 +2113,12 @@
         <v>0.8982</v>
       </c>
       <c r="F53" t="n">
+        <v>1.8431</v>
+      </c>
+      <c r="G53" t="n">
         <v>370.5035</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>609.1301</v>
       </c>
     </row>
@@ -1984,9 +2145,12 @@
         <v>0.8939</v>
       </c>
       <c r="F54" t="n">
+        <v>1.8143</v>
+      </c>
+      <c r="G54" t="n">
         <v>365.4729</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>598.6323</v>
       </c>
     </row>
@@ -2013,9 +2177,12 @@
         <v>0.8898</v>
       </c>
       <c r="F55" t="n">
+        <v>1.9036</v>
+      </c>
+      <c r="G55" t="n">
         <v>372.6439</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>630.5969</v>
       </c>
     </row>
@@ -2042,9 +2209,12 @@
         <v>0.8718</v>
       </c>
       <c r="F56" t="n">
+        <v>1.8997</v>
+      </c>
+      <c r="G56" t="n">
         <v>403.0006</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>629.2388</v>
       </c>
     </row>
@@ -2071,9 +2241,12 @@
         <v>0.8666</v>
       </c>
       <c r="F57" t="n">
+        <v>1.894</v>
+      </c>
+      <c r="G57" t="n">
         <v>399.7901</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>627.2376</v>
       </c>
     </row>
@@ -2100,9 +2273,12 @@
         <v>0.8485</v>
       </c>
       <c r="F58" t="n">
+        <v>1.9574</v>
+      </c>
+      <c r="G58" t="n">
         <v>404.257</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>649.1037</v>
       </c>
     </row>
@@ -2129,9 +2305,12 @@
         <v>0.8448</v>
       </c>
       <c r="F59" t="n">
+        <v>1.9526</v>
+      </c>
+      <c r="G59" t="n">
         <v>405.8213</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>647.4867</v>
       </c>
     </row>
@@ -2158,9 +2337,12 @@
         <v>0.8456</v>
       </c>
       <c r="F60" t="n">
+        <v>1.9508</v>
+      </c>
+      <c r="G60" t="n">
         <v>404.3935</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>646.873</v>
       </c>
     </row>
@@ -2187,9 +2369,12 @@
         <v>0.8658</v>
       </c>
       <c r="F61" t="n">
+        <v>1.9551</v>
+      </c>
+      <c r="G61" t="n">
         <v>384.0545</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>648.3366</v>
       </c>
     </row>
@@ -2216,9 +2401,12 @@
         <v>0.8404</v>
       </c>
       <c r="F62" t="n">
+        <v>1.9411</v>
+      </c>
+      <c r="G62" t="n">
         <v>415.3398</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>643.5527</v>
       </c>
     </row>
@@ -2245,9 +2433,12 @@
         <v>0.8404</v>
       </c>
       <c r="F63" t="n">
+        <v>1.9424</v>
+      </c>
+      <c r="G63" t="n">
         <v>413.7872</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>643.9905</v>
       </c>
     </row>
@@ -2274,9 +2465,12 @@
         <v>0.8372000000000001</v>
       </c>
       <c r="F64" t="n">
+        <v>1.9333</v>
+      </c>
+      <c r="G64" t="n">
         <v>415.9975</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>640.893</v>
       </c>
     </row>
@@ -2303,9 +2497,12 @@
         <v>0.8373</v>
       </c>
       <c r="F65" t="n">
+        <v>1.9247</v>
+      </c>
+      <c r="G65" t="n">
         <v>415.4063</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>637.9189</v>
       </c>
     </row>
@@ -2332,9 +2529,12 @@
         <v>0.8925</v>
       </c>
       <c r="F66" t="n">
+        <v>1.8897</v>
+      </c>
+      <c r="G66" t="n">
         <v>365.9201</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>625.7428</v>
       </c>
     </row>
@@ -2361,9 +2561,12 @@
         <v>0.9026999999999999</v>
       </c>
       <c r="F67" t="n">
+        <v>1.8906</v>
+      </c>
+      <c r="G67" t="n">
         <v>357.9847</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>626.057</v>
       </c>
     </row>
@@ -2390,9 +2593,12 @@
         <v>0.8602</v>
       </c>
       <c r="F68" t="n">
+        <v>1.8989</v>
+      </c>
+      <c r="G68" t="n">
         <v>404.8312</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>628.9651</v>
       </c>
     </row>
@@ -2419,9 +2625,12 @@
         <v>0.9837</v>
       </c>
       <c r="F69" t="n">
+        <v>1.3136</v>
+      </c>
+      <c r="G69" t="n">
         <v>132.2083</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>371.5164</v>
       </c>
     </row>
@@ -2448,9 +2657,12 @@
         <v>0.9849</v>
       </c>
       <c r="F70" t="n">
+        <v>1.3061</v>
+      </c>
+      <c r="G70" t="n">
         <v>129.831</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>367.0531</v>
       </c>
     </row>
@@ -2477,9 +2689,12 @@
         <v>0.9762999999999999</v>
       </c>
       <c r="F71" t="n">
+        <v>1.3322</v>
+      </c>
+      <c r="G71" t="n">
         <v>154.2362</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>382.3624</v>
       </c>
     </row>
@@ -2506,9 +2721,12 @@
         <v>0.9846</v>
       </c>
       <c r="F72" t="n">
+        <v>1.3188</v>
+      </c>
+      <c r="G72" t="n">
         <v>128.6414</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>374.5832</v>
       </c>
     </row>
@@ -2535,9 +2753,12 @@
         <v>0.9534</v>
       </c>
       <c r="F73" t="n">
+        <v>1.352</v>
+      </c>
+      <c r="G73" t="n">
         <v>217.8375</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>393.5632</v>
       </c>
     </row>
@@ -2564,9 +2785,12 @@
         <v>0.9608</v>
       </c>
       <c r="F74" t="n">
+        <v>1.3441</v>
+      </c>
+      <c r="G74" t="n">
         <v>195.7516</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>389.167</v>
       </c>
     </row>
@@ -2593,9 +2817,12 @@
         <v>0.9813</v>
       </c>
       <c r="F75" t="n">
+        <v>1.4031</v>
+      </c>
+      <c r="G75" t="n">
         <v>142.3639</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>421.2</v>
       </c>
     </row>
@@ -2622,9 +2849,12 @@
         <v>0.9813</v>
       </c>
       <c r="F76" t="n">
+        <v>1.4031</v>
+      </c>
+      <c r="G76" t="n">
         <v>142.3639</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>421.2</v>
       </c>
     </row>
@@ -2651,9 +2881,12 @@
         <v>0.8078</v>
       </c>
       <c r="F77" t="n">
+        <v>1.9481</v>
+      </c>
+      <c r="G77" t="n">
         <v>436.2959</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>645.96</v>
       </c>
     </row>
@@ -2680,9 +2913,12 @@
         <v>0.8083</v>
       </c>
       <c r="F78" t="n">
+        <v>1.9464</v>
+      </c>
+      <c r="G78" t="n">
         <v>436.2032</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>645.3871</v>
       </c>
     </row>
@@ -2709,9 +2945,12 @@
         <v>0.8056</v>
       </c>
       <c r="F79" t="n">
+        <v>1.9483</v>
+      </c>
+      <c r="G79" t="n">
         <v>437.057</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>646.0196</v>
       </c>
     </row>
@@ -2738,9 +2977,12 @@
         <v>0.8083</v>
       </c>
       <c r="F80" t="n">
+        <v>1.9464</v>
+      </c>
+      <c r="G80" t="n">
         <v>436.3704</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>645.3563</v>
       </c>
     </row>
@@ -2767,9 +3009,12 @@
         <v>0.8786</v>
       </c>
       <c r="F81" t="n">
+        <v>1.9031</v>
+      </c>
+      <c r="G81" t="n">
         <v>378.13</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>630.4403</v>
       </c>
     </row>
@@ -2796,9 +3041,12 @@
         <v>0.8505</v>
       </c>
       <c r="F82" t="n">
+        <v>1.9153</v>
+      </c>
+      <c r="G82" t="n">
         <v>407.7278</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>634.6656</v>
       </c>
     </row>
@@ -2825,9 +3073,12 @@
         <v>0.9808</v>
       </c>
       <c r="F83" t="n">
+        <v>1.409</v>
+      </c>
+      <c r="G83" t="n">
         <v>143.341</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>424.2604</v>
       </c>
     </row>
@@ -2854,9 +3105,12 @@
         <v>0.9807</v>
       </c>
       <c r="F84" t="n">
+        <v>1.4082</v>
+      </c>
+      <c r="G84" t="n">
         <v>143.6662</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>423.838</v>
       </c>
     </row>
@@ -2883,9 +3137,12 @@
         <v>0.9809</v>
       </c>
       <c r="F85" t="n">
+        <v>1.4108</v>
+      </c>
+      <c r="G85" t="n">
         <v>143.2959</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>425.1692</v>
       </c>
     </row>
@@ -2912,9 +3169,12 @@
         <v>0.9792999999999999</v>
       </c>
       <c r="F86" t="n">
+        <v>1.3388</v>
+      </c>
+      <c r="G86" t="n">
         <v>147.9625</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>386.1339</v>
       </c>
     </row>
@@ -2941,9 +3201,12 @@
         <v>0.9856</v>
       </c>
       <c r="F87" t="n">
+        <v>1.336</v>
+      </c>
+      <c r="G87" t="n">
         <v>129.8917</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>384.5359</v>
       </c>
     </row>
@@ -2970,9 +3233,12 @@
         <v>0.9848</v>
       </c>
       <c r="F88" t="n">
+        <v>1.3388</v>
+      </c>
+      <c r="G88" t="n">
         <v>133.1557</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>386.1375</v>
       </c>
     </row>
@@ -2999,9 +3265,12 @@
         <v>0.9765</v>
       </c>
       <c r="F89" t="n">
+        <v>1.3469</v>
+      </c>
+      <c r="G89" t="n">
         <v>155.3333</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>390.7489</v>
       </c>
     </row>
@@ -3028,9 +3297,12 @@
         <v>0.978</v>
       </c>
       <c r="F90" t="n">
+        <v>1.322</v>
+      </c>
+      <c r="G90" t="n">
         <v>151.8241</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>376.4453</v>
       </c>
     </row>
@@ -3057,9 +3329,12 @@
         <v>0.9859</v>
       </c>
       <c r="F91" t="n">
+        <v>1.3142</v>
+      </c>
+      <c r="G91" t="n">
         <v>125.7703</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>371.8546</v>
       </c>
     </row>
@@ -3086,9 +3361,12 @@
         <v>0.9848</v>
       </c>
       <c r="F92" t="n">
+        <v>1.3388</v>
+      </c>
+      <c r="G92" t="n">
         <v>133.1557</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>386.1375</v>
       </c>
     </row>
@@ -3115,9 +3393,12 @@
         <v>0.9859</v>
       </c>
       <c r="F93" t="n">
+        <v>1.3142</v>
+      </c>
+      <c r="G93" t="n">
         <v>125.7703</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>371.8546</v>
       </c>
     </row>
@@ -3144,9 +3425,12 @@
         <v>0.9815</v>
       </c>
       <c r="F94" t="n">
+        <v>1.4394</v>
+      </c>
+      <c r="G94" t="n">
         <v>147.9455</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>439.7594</v>
       </c>
     </row>
@@ -3173,9 +3457,12 @@
         <v>0.7975</v>
       </c>
       <c r="F95" t="n">
+        <v>2.1466</v>
+      </c>
+      <c r="G95" t="n">
         <v>473.2703</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>710.3605</v>
       </c>
     </row>
@@ -3202,9 +3489,12 @@
         <v>0.9818</v>
       </c>
       <c r="F96" t="n">
+        <v>1.4385</v>
+      </c>
+      <c r="G96" t="n">
         <v>147.0156</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>439.2864</v>
       </c>
     </row>
@@ -3231,9 +3521,12 @@
         <v>0.9819</v>
       </c>
       <c r="F97" t="n">
+        <v>1.4389</v>
+      </c>
+      <c r="G97" t="n">
         <v>146.5793</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>439.5177</v>
       </c>
     </row>
@@ -3260,9 +3553,12 @@
         <v>0.986</v>
       </c>
       <c r="F98" t="n">
+        <v>1.3162</v>
+      </c>
+      <c r="G98" t="n">
         <v>130.6339</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>373.0217</v>
       </c>
     </row>
@@ -3289,9 +3585,12 @@
         <v>0.9847</v>
       </c>
       <c r="F99" t="n">
+        <v>1.3148</v>
+      </c>
+      <c r="G99" t="n">
         <v>133.2663</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>372.1863</v>
       </c>
     </row>
@@ -3318,9 +3617,12 @@
         <v>0.9856</v>
       </c>
       <c r="F100" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G100" t="n">
         <v>130.7212</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>375.2522</v>
       </c>
     </row>
@@ -3347,9 +3649,12 @@
         <v>0.9854000000000001</v>
       </c>
       <c r="F101" t="n">
+        <v>1.322</v>
+      </c>
+      <c r="G101" t="n">
         <v>129.8188</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>376.4327</v>
       </c>
     </row>
@@ -3376,9 +3681,12 @@
         <v>0.9857</v>
       </c>
       <c r="F102" t="n">
+        <v>1.3312</v>
+      </c>
+      <c r="G102" t="n">
         <v>128.3649</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>381.785</v>
       </c>
     </row>
@@ -3405,9 +3713,12 @@
         <v>0.9864000000000001</v>
       </c>
       <c r="F103" t="n">
+        <v>1.3241</v>
+      </c>
+      <c r="G103" t="n">
         <v>129.5243</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>377.6631</v>
       </c>
     </row>
@@ -3434,9 +3745,12 @@
         <v>0.9861</v>
       </c>
       <c r="F104" t="n">
+        <v>1.3194</v>
+      </c>
+      <c r="G104" t="n">
         <v>128.943</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>374.9032</v>
       </c>
     </row>
@@ -3463,9 +3777,12 @@
         <v>0.98</v>
       </c>
       <c r="F105" t="n">
+        <v>1.3165</v>
+      </c>
+      <c r="G105" t="n">
         <v>149.144</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>373.1885</v>
       </c>
     </row>
@@ -3492,9 +3809,12 @@
         <v>0.9842</v>
       </c>
       <c r="F106" t="n">
+        <v>1.3108</v>
+      </c>
+      <c r="G106" t="n">
         <v>133.8707</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>369.8204</v>
       </c>
     </row>
@@ -3521,9 +3841,12 @@
         <v>0.9852</v>
       </c>
       <c r="F107" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="G107" t="n">
         <v>130.7216</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>375.8617</v>
       </c>
     </row>
@@ -3550,9 +3873,12 @@
         <v>0.9857</v>
       </c>
       <c r="F108" t="n">
+        <v>1.368</v>
+      </c>
+      <c r="G108" t="n">
         <v>138.0156</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>402.4533</v>
       </c>
     </row>
@@ -3579,9 +3905,12 @@
         <v>0.982</v>
       </c>
       <c r="F109" t="n">
+        <v>1.3185</v>
+      </c>
+      <c r="G109" t="n">
         <v>146.728</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>374.4102</v>
       </c>
     </row>
@@ -3608,9 +3937,12 @@
         <v>0.9848</v>
       </c>
       <c r="F110" t="n">
+        <v>1.3211</v>
+      </c>
+      <c r="G110" t="n">
         <v>130.263</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>375.9279</v>
       </c>
     </row>
@@ -3637,9 +3969,12 @@
         <v>0.9782999999999999</v>
       </c>
       <c r="F111" t="n">
+        <v>1.3199</v>
+      </c>
+      <c r="G111" t="n">
         <v>153.3862</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>375.2357</v>
       </c>
     </row>
@@ -3666,9 +4001,12 @@
         <v>0.9858</v>
       </c>
       <c r="F112" t="n">
+        <v>1.3631</v>
+      </c>
+      <c r="G112" t="n">
         <v>135.8231</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>399.7492</v>
       </c>
     </row>
@@ -3695,9 +4033,12 @@
         <v>0.9822</v>
       </c>
       <c r="F113" t="n">
+        <v>1.3172</v>
+      </c>
+      <c r="G113" t="n">
         <v>146.349</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>373.6126</v>
       </c>
     </row>
@@ -3724,9 +4065,12 @@
         <v>0.9836</v>
       </c>
       <c r="F114" t="n">
+        <v>1.3176</v>
+      </c>
+      <c r="G114" t="n">
         <v>134.7114</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>373.8665</v>
       </c>
     </row>
@@ -3753,9 +4097,12 @@
         <v>0.978</v>
       </c>
       <c r="F115" t="n">
+        <v>1.3202</v>
+      </c>
+      <c r="G115" t="n">
         <v>154.1862</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>375.3984</v>
       </c>
     </row>
@@ -3782,9 +4129,12 @@
         <v>0.8866000000000001</v>
       </c>
       <c r="F116" t="n">
+        <v>1.9345</v>
+      </c>
+      <c r="G116" t="n">
         <v>364.9176</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>641.3001</v>
       </c>
     </row>
@@ -3811,9 +4161,12 @@
         <v>0.8764999999999999</v>
       </c>
       <c r="F117" t="n">
+        <v>1.9444</v>
+      </c>
+      <c r="G117" t="n">
         <v>371.1572</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>644.6944999999999</v>
       </c>
     </row>
@@ -3840,9 +4193,12 @@
         <v>0.98</v>
       </c>
       <c r="F118" t="n">
+        <v>1.3165</v>
+      </c>
+      <c r="G118" t="n">
         <v>149.144</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>373.1885</v>
       </c>
     </row>
@@ -3869,9 +4225,12 @@
         <v>0.9822</v>
       </c>
       <c r="F119" t="n">
+        <v>1.3172</v>
+      </c>
+      <c r="G119" t="n">
         <v>146.349</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>373.6126</v>
       </c>
     </row>
@@ -3898,9 +4257,12 @@
         <v>0.9363</v>
       </c>
       <c r="F120" t="n">
+        <v>1.3472</v>
+      </c>
+      <c r="G120" t="n">
         <v>239.9007</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>390.8713</v>
       </c>
     </row>
@@ -3927,9 +4289,12 @@
         <v>0.9363</v>
       </c>
       <c r="F121" t="n">
+        <v>1.3472</v>
+      </c>
+      <c r="G121" t="n">
         <v>239.9007</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>390.8713</v>
       </c>
     </row>
@@ -3956,9 +4321,12 @@
         <v>0.9744</v>
       </c>
       <c r="F122" t="n">
+        <v>1.2869</v>
+      </c>
+      <c r="G122" t="n">
         <v>155.3144</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>355.3553</v>
       </c>
     </row>
@@ -3985,9 +4353,12 @@
         <v>0.9821</v>
       </c>
       <c r="F123" t="n">
+        <v>1.3171</v>
+      </c>
+      <c r="G123" t="n">
         <v>146.8122</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>373.5886</v>
       </c>
     </row>
@@ -4014,9 +4385,12 @@
         <v>0.9781</v>
       </c>
       <c r="F124" t="n">
+        <v>1.3301</v>
+      </c>
+      <c r="G124" t="n">
         <v>159.782</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>381.1461</v>
       </c>
     </row>
@@ -4043,9 +4417,12 @@
         <v>0.9812</v>
       </c>
       <c r="F125" t="n">
+        <v>1.443</v>
+      </c>
+      <c r="G125" t="n">
         <v>148.5925</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>441.527</v>
       </c>
     </row>
@@ -4072,9 +4449,12 @@
         <v>0.9801</v>
       </c>
       <c r="F126" t="n">
+        <v>1.3242</v>
+      </c>
+      <c r="G126" t="n">
         <v>145.2877</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>377.7509</v>
       </c>
     </row>
@@ -4101,9 +4481,12 @@
         <v>0.8449</v>
       </c>
       <c r="F127" t="n">
+        <v>2.0207</v>
+      </c>
+      <c r="G127" t="n">
         <v>411.4272</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>670.217</v>
       </c>
     </row>
@@ -4130,9 +4513,12 @@
         <v>0.9854000000000001</v>
       </c>
       <c r="F128" t="n">
+        <v>1.3389</v>
+      </c>
+      <c r="G128" t="n">
         <v>130.3922</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>386.1908</v>
       </c>
     </row>
@@ -4159,9 +4545,12 @@
         <v>0.9858</v>
       </c>
       <c r="F129" t="n">
+        <v>1.3385</v>
+      </c>
+      <c r="G129" t="n">
         <v>129.2235</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>385.9443</v>
       </c>
     </row>
@@ -4188,9 +4577,12 @@
         <v>0.985</v>
       </c>
       <c r="F130" t="n">
+        <v>1.3381</v>
+      </c>
+      <c r="G130" t="n">
         <v>129.3455</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>385.7534</v>
       </c>
     </row>
@@ -4217,9 +4609,12 @@
         <v>0.9854000000000001</v>
       </c>
       <c r="F131" t="n">
+        <v>1.3436</v>
+      </c>
+      <c r="G131" t="n">
         <v>129.8148</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>388.8385</v>
       </c>
     </row>
@@ -4246,9 +4641,12 @@
         <v>0.9794</v>
       </c>
       <c r="F132" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="G132" t="n">
         <v>147.1833</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>382.8252</v>
       </c>
     </row>
@@ -4275,9 +4673,12 @@
         <v>0.9789</v>
       </c>
       <c r="F133" t="n">
+        <v>1.3334</v>
+      </c>
+      <c r="G133" t="n">
         <v>148.5293</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>383.0337</v>
       </c>
     </row>
@@ -4304,9 +4705,12 @@
         <v>0.9784</v>
       </c>
       <c r="F134" t="n">
+        <v>1.3342</v>
+      </c>
+      <c r="G134" t="n">
         <v>150.0476</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>383.519</v>
       </c>
     </row>
@@ -4333,9 +4737,12 @@
         <v>0.9858</v>
       </c>
       <c r="F135" t="n">
+        <v>1.3377</v>
+      </c>
+      <c r="G135" t="n">
         <v>129.0591</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>385.4843</v>
       </c>
     </row>
@@ -4362,9 +4769,12 @@
         <v>0.9857</v>
       </c>
       <c r="F136" t="n">
+        <v>1.3403</v>
+      </c>
+      <c r="G136" t="n">
         <v>128.563</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>387.002</v>
       </c>
     </row>
@@ -4391,9 +4801,12 @@
         <v>0.9807</v>
       </c>
       <c r="F137" t="n">
+        <v>1.3132</v>
+      </c>
+      <c r="G137" t="n">
         <v>141.863</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>371.2664</v>
       </c>
     </row>
@@ -4420,9 +4833,12 @@
         <v>0.9759</v>
       </c>
       <c r="F138" t="n">
+        <v>1.3132</v>
+      </c>
+      <c r="G138" t="n">
         <v>156.4093</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>371.2769</v>
       </c>
     </row>
@@ -4449,9 +4865,12 @@
         <v>0.9805</v>
       </c>
       <c r="F139" t="n">
+        <v>1.3133</v>
+      </c>
+      <c r="G139" t="n">
         <v>142.4346</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>371.3006</v>
       </c>
     </row>
@@ -4478,9 +4897,12 @@
         <v>0.9852</v>
       </c>
       <c r="F140" t="n">
+        <v>1.2998</v>
+      </c>
+      <c r="G140" t="n">
         <v>129.0378</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>363.254</v>
       </c>
     </row>
@@ -4507,9 +4929,12 @@
         <v>0.9857</v>
       </c>
       <c r="F141" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="G141" t="n">
         <v>127.3827</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>360.3129</v>
       </c>
     </row>
@@ -4536,9 +4961,12 @@
         <v>0.9759</v>
       </c>
       <c r="F142" t="n">
+        <v>1.3132</v>
+      </c>
+      <c r="G142" t="n">
         <v>156.4093</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>371.2769</v>
       </c>
     </row>
@@ -4565,9 +4993,12 @@
         <v>0.9782999999999999</v>
       </c>
       <c r="F143" t="n">
+        <v>1.3127</v>
+      </c>
+      <c r="G143" t="n">
         <v>149.5814</v>
       </c>
-      <c r="G143" t="n">
+      <c r="H143" t="n">
         <v>370.9851</v>
       </c>
     </row>
@@ -4594,9 +5025,12 @@
         <v>0.9791</v>
       </c>
       <c r="F144" t="n">
+        <v>1.3087</v>
+      </c>
+      <c r="G144" t="n">
         <v>144.9349</v>
       </c>
-      <c r="G144" t="n">
+      <c r="H144" t="n">
         <v>368.6119</v>
       </c>
     </row>
@@ -4623,9 +5057,12 @@
         <v>0.9857</v>
       </c>
       <c r="F145" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="G145" t="n">
         <v>127.3827</v>
       </c>
-      <c r="G145" t="n">
+      <c r="H145" t="n">
         <v>360.3129</v>
       </c>
     </row>
@@ -4652,9 +5089,12 @@
         <v>0.8467</v>
       </c>
       <c r="F146" t="n">
+        <v>2.0107</v>
+      </c>
+      <c r="G146" t="n">
         <v>412.102</v>
       </c>
-      <c r="G146" t="n">
+      <c r="H146" t="n">
         <v>666.9450000000001</v>
       </c>
     </row>
@@ -4681,9 +5121,12 @@
         <v>0.8487</v>
       </c>
       <c r="F147" t="n">
+        <v>2.0157</v>
+      </c>
+      <c r="G147" t="n">
         <v>409.4122</v>
       </c>
-      <c r="G147" t="n">
+      <c r="H147" t="n">
         <v>668.597</v>
       </c>
     </row>
@@ -4710,9 +5153,12 @@
         <v>0.8445</v>
       </c>
       <c r="F148" t="n">
+        <v>2.0155</v>
+      </c>
+      <c r="G148" t="n">
         <v>413.5223</v>
       </c>
-      <c r="G148" t="n">
+      <c r="H148" t="n">
         <v>668.5302</v>
       </c>
     </row>
@@ -4739,9 +5185,12 @@
         <v>0.8437</v>
       </c>
       <c r="F149" t="n">
+        <v>2.0176</v>
+      </c>
+      <c r="G149" t="n">
         <v>413.7097</v>
       </c>
-      <c r="G149" t="n">
+      <c r="H149" t="n">
         <v>669.2008</v>
       </c>
     </row>
@@ -4768,9 +5217,12 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="F150" t="n">
+        <v>2.0148</v>
+      </c>
+      <c r="G150" t="n">
         <v>410.2758</v>
       </c>
-      <c r="G150" t="n">
+      <c r="H150" t="n">
         <v>668.3015</v>
       </c>
     </row>
@@ -4797,9 +5249,12 @@
         <v>0.8467</v>
       </c>
       <c r="F151" t="n">
+        <v>2.0179</v>
+      </c>
+      <c r="G151" t="n">
         <v>409.413</v>
       </c>
-      <c r="G151" t="n">
+      <c r="H151" t="n">
         <v>669.2895</v>
       </c>
     </row>
@@ -4826,9 +5281,12 @@
         <v>0.8468</v>
       </c>
       <c r="F152" t="n">
+        <v>2.0191</v>
+      </c>
+      <c r="G152" t="n">
         <v>410.5961</v>
       </c>
-      <c r="G152" t="n">
+      <c r="H152" t="n">
         <v>669.7025</v>
       </c>
     </row>
@@ -4855,9 +5313,12 @@
         <v>0.8435</v>
       </c>
       <c r="F153" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="G153" t="n">
         <v>413.7241</v>
       </c>
-      <c r="G153" t="n">
+      <c r="H153" t="n">
         <v>668.6964</v>
       </c>
     </row>
@@ -4884,9 +5345,12 @@
         <v>0.8468</v>
       </c>
       <c r="F154" t="n">
+        <v>2.0159</v>
+      </c>
+      <c r="G154" t="n">
         <v>411.9744</v>
       </c>
-      <c r="G154" t="n">
+      <c r="H154" t="n">
         <v>668.6466</v>
       </c>
     </row>
@@ -4913,9 +5377,12 @@
         <v>0.8822</v>
       </c>
       <c r="F155" t="n">
+        <v>1.9202</v>
+      </c>
+      <c r="G155" t="n">
         <v>382.0004</v>
       </c>
-      <c r="G155" t="n">
+      <c r="H155" t="n">
         <v>636.3786</v>
       </c>
     </row>
@@ -4942,9 +5409,12 @@
         <v>0.844</v>
       </c>
       <c r="F156" t="n">
+        <v>1.9412</v>
+      </c>
+      <c r="G156" t="n">
         <v>415.492</v>
       </c>
-      <c r="G156" t="n">
+      <c r="H156" t="n">
         <v>643.5905</v>
       </c>
     </row>
@@ -4971,9 +5441,12 @@
         <v>0.8617</v>
       </c>
       <c r="F157" t="n">
+        <v>1.9329</v>
+      </c>
+      <c r="G157" t="n">
         <v>399.1334</v>
       </c>
-      <c r="G157" t="n">
+      <c r="H157" t="n">
         <v>640.7482</v>
       </c>
     </row>
@@ -5000,9 +5473,12 @@
         <v>0.8575</v>
       </c>
       <c r="F158" t="n">
+        <v>1.8937</v>
+      </c>
+      <c r="G158" t="n">
         <v>410.2638</v>
       </c>
-      <c r="G158" t="n">
+      <c r="H158" t="n">
         <v>627.1333</v>
       </c>
     </row>
@@ -5029,9 +5505,12 @@
         <v>0.9786</v>
       </c>
       <c r="F159" t="n">
+        <v>1.2978</v>
+      </c>
+      <c r="G159" t="n">
         <v>145.9842</v>
       </c>
-      <c r="G159" t="n">
+      <c r="H159" t="n">
         <v>362.0362</v>
       </c>
     </row>
@@ -5058,9 +5537,12 @@
         <v>0.8078</v>
       </c>
       <c r="F160" t="n">
+        <v>2.0026</v>
+      </c>
+      <c r="G160" t="n">
         <v>449.6392</v>
       </c>
-      <c r="G160" t="n">
+      <c r="H160" t="n">
         <v>664.2560999999999</v>
       </c>
     </row>
@@ -5087,9 +5569,12 @@
         <v>0.8455</v>
       </c>
       <c r="F161" t="n">
+        <v>2.0032</v>
+      </c>
+      <c r="G161" t="n">
         <v>414.278</v>
       </c>
-      <c r="G161" t="n">
+      <c r="H161" t="n">
         <v>664.4628</v>
       </c>
     </row>
@@ -5116,9 +5601,12 @@
         <v>0.978</v>
       </c>
       <c r="F162" t="n">
+        <v>1.3082</v>
+      </c>
+      <c r="G162" t="n">
         <v>148.4737</v>
       </c>
-      <c r="G162" t="n">
+      <c r="H162" t="n">
         <v>368.2855</v>
       </c>
     </row>
@@ -5145,9 +5633,12 @@
         <v>0.9845</v>
       </c>
       <c r="F163" t="n">
+        <v>1.3233</v>
+      </c>
+      <c r="G163" t="n">
         <v>129.1146</v>
       </c>
-      <c r="G163" t="n">
+      <c r="H163" t="n">
         <v>377.2004</v>
       </c>
     </row>
@@ -5174,9 +5665,12 @@
         <v>0.9852</v>
       </c>
       <c r="F164" t="n">
+        <v>1.3012</v>
+      </c>
+      <c r="G164" t="n">
         <v>129.1936</v>
       </c>
-      <c r="G164" t="n">
+      <c r="H164" t="n">
         <v>364.0913</v>
       </c>
     </row>
@@ -5203,9 +5697,12 @@
         <v>0.9812</v>
       </c>
       <c r="F165" t="n">
+        <v>1.443</v>
+      </c>
+      <c r="G165" t="n">
         <v>148.5925</v>
       </c>
-      <c r="G165" t="n">
+      <c r="H165" t="n">
         <v>441.527</v>
       </c>
     </row>
@@ -5232,9 +5729,12 @@
         <v>0.7924</v>
       </c>
       <c r="F166" t="n">
+        <v>2.1468</v>
+      </c>
+      <c r="G166" t="n">
         <v>474.0217</v>
       </c>
-      <c r="G166" t="n">
+      <c r="H166" t="n">
         <v>710.4115</v>
       </c>
     </row>
@@ -5261,9 +5761,12 @@
         <v>0.9781</v>
       </c>
       <c r="F167" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="G167" t="n">
         <v>151.5051</v>
       </c>
-      <c r="G167" t="n">
+      <c r="H167" t="n">
         <v>359.715</v>
       </c>
     </row>
@@ -5290,9 +5793,12 @@
         <v>0.986</v>
       </c>
       <c r="F168" t="n">
+        <v>1.2783</v>
+      </c>
+      <c r="G168" t="n">
         <v>125.1871</v>
       </c>
-      <c r="G168" t="n">
+      <c r="H168" t="n">
         <v>349.9414</v>
       </c>
     </row>
@@ -5319,9 +5825,12 @@
         <v>0.9752</v>
       </c>
       <c r="F169" t="n">
+        <v>1.3423</v>
+      </c>
+      <c r="G169" t="n">
         <v>158.9385</v>
       </c>
-      <c r="G169" t="n">
+      <c r="H169" t="n">
         <v>388.1476</v>
       </c>
     </row>
@@ -5348,9 +5857,12 @@
         <v>0.9839</v>
       </c>
       <c r="F170" t="n">
+        <v>1.3678</v>
+      </c>
+      <c r="G170" t="n">
         <v>137.8683</v>
       </c>
-      <c r="G170" t="n">
+      <c r="H170" t="n">
         <v>402.3166</v>
       </c>
     </row>
@@ -5377,9 +5889,12 @@
         <v>0.9772</v>
       </c>
       <c r="F171" t="n">
+        <v>1.3102</v>
+      </c>
+      <c r="G171" t="n">
         <v>156.5498</v>
       </c>
-      <c r="G171" t="n">
+      <c r="H171" t="n">
         <v>369.4755</v>
       </c>
     </row>
@@ -5406,9 +5921,12 @@
         <v>0.98</v>
       </c>
       <c r="F172" t="n">
+        <v>1.2984</v>
+      </c>
+      <c r="G172" t="n">
         <v>143.5005</v>
       </c>
-      <c r="G172" t="n">
+      <c r="H172" t="n">
         <v>362.3605</v>
       </c>
     </row>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
@@ -478,16 +478,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9781</v>
+        <v>0.9694</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3444</v>
+        <v>0.6601</v>
       </c>
       <c r="G2" t="n">
-        <v>148.6799</v>
+        <v>170.3993</v>
       </c>
       <c r="H2" t="n">
-        <v>389.328</v>
+        <v>377.5411</v>
       </c>
     </row>
     <row r="3">
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9796</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3267</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>145.1952</v>
+        <v>145.643</v>
       </c>
       <c r="H3" t="n">
-        <v>379.1894</v>
+        <v>351.6789</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9815</v>
+        <v>0.9404</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4394</v>
+        <v>0.6208</v>
       </c>
       <c r="G4" t="n">
-        <v>147.9455</v>
+        <v>229.1853</v>
       </c>
       <c r="H4" t="n">
-        <v>439.7594</v>
+        <v>398.7601</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8661</v>
+        <v>0.8524</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9451</v>
+        <v>-0.0451</v>
       </c>
       <c r="G5" t="n">
-        <v>383.2601</v>
+        <v>400.7203</v>
       </c>
       <c r="H5" t="n">
-        <v>644.943</v>
+        <v>662.0218</v>
       </c>
     </row>
     <row r="6">
@@ -602,20 +602,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8495</v>
+        <v>0.8718</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9572</v>
+        <v>-0.0495</v>
       </c>
       <c r="G6" t="n">
-        <v>403.685</v>
+        <v>383.0446</v>
       </c>
       <c r="H6" t="n">
-        <v>649.0386999999999</v>
+        <v>663.4172</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9789</v>
+        <v>0.9423</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3719</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>146.3999</v>
+        <v>224.4757</v>
       </c>
       <c r="H7" t="n">
-        <v>404.5824</v>
+        <v>424.5971</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9843</v>
+        <v>0.9704</v>
       </c>
       <c r="F8" t="n">
-        <v>1.373</v>
+        <v>0.6277</v>
       </c>
       <c r="G8" t="n">
-        <v>133.7186</v>
+        <v>168.2466</v>
       </c>
       <c r="H8" t="n">
-        <v>405.1676</v>
+        <v>395.1264</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9812</v>
+        <v>0.9833</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3183</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>139.1883</v>
+        <v>131.7469</v>
       </c>
       <c r="H9" t="n">
-        <v>374.2521</v>
+        <v>347.4227</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9843</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3694</v>
+        <v>0.632</v>
       </c>
       <c r="G10" t="n">
-        <v>133.134</v>
+        <v>146.1113</v>
       </c>
       <c r="H10" t="n">
-        <v>403.194</v>
+        <v>392.8224</v>
       </c>
     </row>
     <row r="11">
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9838</v>
+        <v>0.981</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3685</v>
+        <v>0.625</v>
       </c>
       <c r="G11" t="n">
-        <v>134.671</v>
+        <v>143.1245</v>
       </c>
       <c r="H11" t="n">
-        <v>402.6887</v>
+        <v>396.564</v>
       </c>
     </row>
     <row r="12">
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9841</v>
+        <v>0.9811</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3684</v>
+        <v>0.6213</v>
       </c>
       <c r="G12" t="n">
-        <v>134.2288</v>
+        <v>143.0885</v>
       </c>
       <c r="H12" t="n">
-        <v>402.6543</v>
+        <v>398.522</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9836</v>
+        <v>0.9692</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3725</v>
+        <v>0.6303</v>
       </c>
       <c r="G13" t="n">
-        <v>135.6569</v>
+        <v>174.1433</v>
       </c>
       <c r="H13" t="n">
-        <v>404.875</v>
+        <v>393.7504</v>
       </c>
     </row>
     <row r="14">
@@ -862,16 +862,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9839</v>
+        <v>0.981</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3674</v>
+        <v>0.6249</v>
       </c>
       <c r="G14" t="n">
-        <v>134.6545</v>
+        <v>143.1205</v>
       </c>
       <c r="H14" t="n">
-        <v>402.0988</v>
+        <v>396.6285</v>
       </c>
     </row>
     <row r="15">
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9841</v>
+        <v>0.9813</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3659</v>
+        <v>0.6233</v>
       </c>
       <c r="G15" t="n">
-        <v>134.5873</v>
+        <v>142.4001</v>
       </c>
       <c r="H15" t="n">
-        <v>401.3086</v>
+        <v>397.4864</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9841</v>
+        <v>0.9792</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3637</v>
+        <v>0.6304</v>
       </c>
       <c r="G16" t="n">
-        <v>134.9514</v>
+        <v>145.2793</v>
       </c>
       <c r="H16" t="n">
-        <v>400.0793</v>
+        <v>393.7219</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9837</v>
+        <v>0.9688</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3684</v>
+        <v>0.633</v>
       </c>
       <c r="G17" t="n">
-        <v>135.197</v>
+        <v>174.5804</v>
       </c>
       <c r="H17" t="n">
-        <v>402.6765</v>
+        <v>392.3123</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9846</v>
+        <v>0.9714</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3168</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>128.6686</v>
+        <v>164.3521</v>
       </c>
       <c r="H18" t="n">
-        <v>373.3626</v>
+        <v>369.2353</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9785</v>
+        <v>0.9786</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3132</v>
+        <v>0.6849</v>
       </c>
       <c r="G19" t="n">
-        <v>147.1401</v>
+        <v>145.671</v>
       </c>
       <c r="H19" t="n">
-        <v>371.2747</v>
+        <v>363.5196</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9841</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3155</v>
+        <v>0.668</v>
       </c>
       <c r="G20" t="n">
-        <v>132.6741</v>
+        <v>151.9274</v>
       </c>
       <c r="H20" t="n">
-        <v>372.652</v>
+        <v>373.1147</v>
       </c>
     </row>
     <row r="21">
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9852</v>
+        <v>0.9777</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3154</v>
+        <v>0.6672</v>
       </c>
       <c r="G21" t="n">
-        <v>128.0559</v>
+        <v>146.6934</v>
       </c>
       <c r="H21" t="n">
-        <v>372.561</v>
+        <v>373.558</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9859</v>
+        <v>0.9724</v>
       </c>
       <c r="F22" t="n">
-        <v>1.313</v>
+        <v>0.6573</v>
       </c>
       <c r="G22" t="n">
-        <v>127.4023</v>
+        <v>161.9804</v>
       </c>
       <c r="H22" t="n">
-        <v>371.1678</v>
+        <v>379.0776</v>
       </c>
     </row>
     <row r="23">
@@ -1150,16 +1150,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9848</v>
+        <v>0.9802</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3229</v>
+        <v>0.656</v>
       </c>
       <c r="G23" t="n">
-        <v>129.4109</v>
+        <v>146.4201</v>
       </c>
       <c r="H23" t="n">
-        <v>376.9555</v>
+        <v>379.8339</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.984</v>
+        <v>0.9801</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3306</v>
+        <v>0.6622</v>
       </c>
       <c r="G24" t="n">
-        <v>133.5638</v>
+        <v>144.1567</v>
       </c>
       <c r="H24" t="n">
-        <v>381.4212</v>
+        <v>376.4038</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9838</v>
+        <v>0.9809</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3335</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>134.1507</v>
+        <v>142.0918</v>
       </c>
       <c r="H25" t="n">
-        <v>383.126</v>
+        <v>377.7364</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9798</v>
+        <v>0.9785</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3289</v>
+        <v>0.6803</v>
       </c>
       <c r="G26" t="n">
-        <v>145.5075</v>
+        <v>145.4241</v>
       </c>
       <c r="H26" t="n">
-        <v>380.4556</v>
+        <v>366.1327</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9795</v>
+        <v>0.9787</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3124</v>
+        <v>0.6746</v>
       </c>
       <c r="G27" t="n">
-        <v>143.722</v>
+        <v>143.764</v>
       </c>
       <c r="H27" t="n">
-        <v>370.7932</v>
+        <v>369.4267</v>
       </c>
     </row>
     <row r="28">
@@ -1310,16 +1310,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9804</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3127</v>
+        <v>0.6849</v>
       </c>
       <c r="G28" t="n">
-        <v>142.623</v>
+        <v>162.6121</v>
       </c>
       <c r="H28" t="n">
-        <v>370.9471</v>
+        <v>363.527</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9784</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3174</v>
+        <v>0.6735</v>
       </c>
       <c r="G29" t="n">
-        <v>129.2974</v>
+        <v>145.8227</v>
       </c>
       <c r="H29" t="n">
-        <v>373.7567</v>
+        <v>370.013</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9852</v>
+        <v>0.9777</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3178</v>
+        <v>0.6624</v>
       </c>
       <c r="G30" t="n">
-        <v>132.2402</v>
+        <v>149.0129</v>
       </c>
       <c r="H30" t="n">
-        <v>373.9786</v>
+        <v>376.2575</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9786</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3117</v>
+        <v>0.6703</v>
       </c>
       <c r="G31" t="n">
-        <v>151.2289</v>
+        <v>145.6313</v>
       </c>
       <c r="H31" t="n">
-        <v>370.3915</v>
+        <v>371.8172</v>
       </c>
     </row>
     <row r="32">
@@ -1438,16 +1438,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9855</v>
+        <v>0.977</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3142</v>
+        <v>0.661</v>
       </c>
       <c r="G32" t="n">
-        <v>124.6297</v>
+        <v>150.5213</v>
       </c>
       <c r="H32" t="n">
-        <v>371.8649</v>
+        <v>377.0592</v>
       </c>
     </row>
     <row r="33">
@@ -1470,16 +1470,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9839</v>
+        <v>0.9771</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3101</v>
+        <v>0.6679</v>
       </c>
       <c r="G33" t="n">
-        <v>129.9522</v>
+        <v>151.316</v>
       </c>
       <c r="H33" t="n">
-        <v>369.45</v>
+        <v>373.175</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9866</v>
+        <v>0.9671</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3146</v>
+        <v>0.6919</v>
       </c>
       <c r="G34" t="n">
-        <v>121.9888</v>
+        <v>176.7888</v>
       </c>
       <c r="H34" t="n">
-        <v>372.0681</v>
+        <v>359.4703</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9821</v>
+        <v>0.9741</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2987</v>
+        <v>0.7108</v>
       </c>
       <c r="G35" t="n">
-        <v>138.2053</v>
+        <v>157.1314</v>
       </c>
       <c r="H35" t="n">
-        <v>362.577</v>
+        <v>348.2327</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9785</v>
+        <v>0.9816</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3233</v>
+        <v>0.7136</v>
       </c>
       <c r="G36" t="n">
-        <v>150.8142</v>
+        <v>134.9828</v>
       </c>
       <c r="H36" t="n">
-        <v>377.1881</v>
+        <v>346.5539</v>
       </c>
     </row>
     <row r="37">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9853</v>
+        <v>0.9818</v>
       </c>
       <c r="F37" t="n">
-        <v>1.3133</v>
+        <v>0.7147</v>
       </c>
       <c r="G37" t="n">
-        <v>127.7184</v>
+        <v>137.6826</v>
       </c>
       <c r="H37" t="n">
-        <v>371.2995</v>
+        <v>345.9153</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9848</v>
+        <v>0.976</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3029</v>
+        <v>0.7204</v>
       </c>
       <c r="G38" t="n">
-        <v>124.868</v>
+        <v>150.2634</v>
       </c>
       <c r="H38" t="n">
-        <v>365.1128</v>
+        <v>342.4533</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9843</v>
+        <v>0.9771</v>
       </c>
       <c r="F39" t="n">
-        <v>1.2965</v>
+        <v>0.7315</v>
       </c>
       <c r="G39" t="n">
-        <v>123.6423</v>
+        <v>148.3768</v>
       </c>
       <c r="H39" t="n">
-        <v>361.2594</v>
+        <v>335.541</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9855</v>
+        <v>0.9779</v>
       </c>
       <c r="F40" t="n">
-        <v>1.3033</v>
+        <v>0.7141</v>
       </c>
       <c r="G40" t="n">
-        <v>119.4004</v>
+        <v>144.4123</v>
       </c>
       <c r="H40" t="n">
-        <v>365.3393</v>
+        <v>346.2577</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9816</v>
+        <v>0.9676</v>
       </c>
       <c r="F41" t="n">
-        <v>1.3131</v>
+        <v>0.6927</v>
       </c>
       <c r="G41" t="n">
-        <v>141.509</v>
+        <v>175.7874</v>
       </c>
       <c r="H41" t="n">
-        <v>371.1946</v>
+        <v>358.9593</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9819</v>
+        <v>0.9748</v>
       </c>
       <c r="F42" t="n">
-        <v>1.2985</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>139.0419</v>
+        <v>155.8159</v>
       </c>
       <c r="H42" t="n">
-        <v>362.435</v>
+        <v>350.395</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.978</v>
+        <v>0.9657</v>
       </c>
       <c r="F43" t="n">
-        <v>1.3214</v>
+        <v>0.7115</v>
       </c>
       <c r="G43" t="n">
-        <v>151.8265</v>
+        <v>180.0428</v>
       </c>
       <c r="H43" t="n">
-        <v>376.1177</v>
+        <v>347.8125</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9859</v>
+        <v>0.9786</v>
       </c>
       <c r="F44" t="n">
-        <v>1.3148</v>
+        <v>0.7089</v>
       </c>
       <c r="G44" t="n">
-        <v>125.7703</v>
+        <v>144.1424</v>
       </c>
       <c r="H44" t="n">
-        <v>372.2289</v>
+        <v>349.3893</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.985</v>
+        <v>0.9819</v>
       </c>
       <c r="F45" t="n">
-        <v>1.3004</v>
+        <v>0.7145</v>
       </c>
       <c r="G45" t="n">
-        <v>123.5471</v>
+        <v>135.586</v>
       </c>
       <c r="H45" t="n">
-        <v>363.58</v>
+        <v>346.047</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9846</v>
+        <v>0.9765</v>
       </c>
       <c r="F46" t="n">
-        <v>1.2974</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>122.7241</v>
+        <v>149.6509</v>
       </c>
       <c r="H46" t="n">
-        <v>361.7853</v>
+        <v>338.1697</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9749</v>
       </c>
       <c r="F47" t="n">
-        <v>1.3013</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>120.4483</v>
+        <v>155.7013</v>
       </c>
       <c r="H47" t="n">
-        <v>364.1237</v>
+        <v>345.5772</v>
       </c>
     </row>
     <row r="48">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9665</v>
       </c>
       <c r="F48" t="n">
-        <v>1.3407</v>
+        <v>0.7114</v>
       </c>
       <c r="G48" t="n">
-        <v>156.8704</v>
+        <v>178.3119</v>
       </c>
       <c r="H48" t="n">
-        <v>387.241</v>
+        <v>347.8794</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9875</v>
+        <v>0.9666</v>
       </c>
       <c r="F49" t="n">
-        <v>1.3195</v>
+        <v>0.7167</v>
       </c>
       <c r="G49" t="n">
-        <v>125.3158</v>
+        <v>177.1281</v>
       </c>
       <c r="H49" t="n">
-        <v>375.0064</v>
+        <v>344.7116</v>
       </c>
     </row>
     <row r="50">
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.8627</v>
+        <v>0.8757</v>
       </c>
       <c r="F50" t="n">
-        <v>1.9031</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>401.4208</v>
+        <v>390.9935</v>
       </c>
       <c r="H50" t="n">
-        <v>630.4257</v>
+        <v>622.7219</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8757</v>
+        <v>0.975</v>
       </c>
       <c r="F51" t="n">
-        <v>1.8859</v>
+        <v>0.1156</v>
       </c>
       <c r="G51" t="n">
-        <v>391.1494</v>
+        <v>229.0176</v>
       </c>
       <c r="H51" t="n">
-        <v>624.3948</v>
+        <v>608.9987</v>
       </c>
     </row>
     <row r="52">
@@ -2078,16 +2078,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.8968</v>
       </c>
       <c r="F52" t="n">
-        <v>1.8772</v>
+        <v>0.1106</v>
       </c>
       <c r="G52" t="n">
-        <v>374.5973</v>
+        <v>367.6504</v>
       </c>
       <c r="H52" t="n">
-        <v>621.3458000000001</v>
+        <v>610.7282</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.8982</v>
+        <v>0.9665</v>
       </c>
       <c r="F53" t="n">
-        <v>1.8431</v>
+        <v>0.183</v>
       </c>
       <c r="G53" t="n">
-        <v>370.5035</v>
+        <v>258.5707</v>
       </c>
       <c r="H53" t="n">
-        <v>609.1301</v>
+        <v>585.3253</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8939</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>1.8143</v>
+        <v>0.2179</v>
       </c>
       <c r="G54" t="n">
-        <v>365.4729</v>
+        <v>311.4605</v>
       </c>
       <c r="H54" t="n">
-        <v>598.6323</v>
+        <v>572.6887</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8898</v>
+        <v>0.8894</v>
       </c>
       <c r="F55" t="n">
-        <v>1.9036</v>
+        <v>0.0128</v>
       </c>
       <c r="G55" t="n">
-        <v>372.6439</v>
+        <v>385.5496</v>
       </c>
       <c r="H55" t="n">
-        <v>630.5969</v>
+        <v>643.4238</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.8718</v>
+        <v>0.9034</v>
       </c>
       <c r="F56" t="n">
-        <v>1.8997</v>
+        <v>0.0578</v>
       </c>
       <c r="G56" t="n">
-        <v>403.0006</v>
+        <v>378.0123</v>
       </c>
       <c r="H56" t="n">
-        <v>629.2388</v>
+        <v>628.582</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.8666</v>
+        <v>0.9552</v>
       </c>
       <c r="F57" t="n">
-        <v>1.894</v>
+        <v>0.0605</v>
       </c>
       <c r="G57" t="n">
-        <v>399.7901</v>
+        <v>284.5113</v>
       </c>
       <c r="H57" t="n">
-        <v>627.2376</v>
+        <v>627.6765</v>
       </c>
     </row>
     <row r="58">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8485</v>
+        <v>0.8914</v>
       </c>
       <c r="F58" t="n">
-        <v>1.9574</v>
+        <v>-0.0446</v>
       </c>
       <c r="G58" t="n">
-        <v>404.257</v>
+        <v>359.2025</v>
       </c>
       <c r="H58" t="n">
-        <v>649.1037</v>
+        <v>661.8552</v>
       </c>
     </row>
     <row r="59">
@@ -2298,20 +2298,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8448</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>1.9526</v>
+        <v>-0.0466</v>
       </c>
       <c r="G59" t="n">
-        <v>405.8213</v>
+        <v>371.5026</v>
       </c>
       <c r="H59" t="n">
-        <v>647.4867</v>
+        <v>662.5123</v>
       </c>
     </row>
     <row r="60">
@@ -2330,20 +2330,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8456</v>
+        <v>0.9635</v>
       </c>
       <c r="F60" t="n">
-        <v>1.9508</v>
+        <v>-0.0336</v>
       </c>
       <c r="G60" t="n">
-        <v>404.3935</v>
+        <v>246.9754</v>
       </c>
       <c r="H60" t="n">
-        <v>646.873</v>
+        <v>658.3638999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2362,20 +2362,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8658</v>
+        <v>0.9646</v>
       </c>
       <c r="F61" t="n">
-        <v>1.9551</v>
+        <v>-0.0237</v>
       </c>
       <c r="G61" t="n">
-        <v>384.0545</v>
+        <v>244.7669</v>
       </c>
       <c r="H61" t="n">
-        <v>648.3366</v>
+        <v>655.1994999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2394,20 +2394,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8404</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>1.9411</v>
+        <v>0.0353</v>
       </c>
       <c r="G62" t="n">
-        <v>415.3398</v>
+        <v>374.3398</v>
       </c>
       <c r="H62" t="n">
-        <v>643.5527</v>
+        <v>636.0471</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8404</v>
+        <v>0.8871</v>
       </c>
       <c r="F63" t="n">
-        <v>1.9424</v>
+        <v>0.0335</v>
       </c>
       <c r="G63" t="n">
-        <v>413.7872</v>
+        <v>376.8271</v>
       </c>
       <c r="H63" t="n">
-        <v>643.9905</v>
+        <v>636.6559</v>
       </c>
     </row>
     <row r="64">
@@ -2458,20 +2458,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.8825</v>
       </c>
       <c r="F64" t="n">
-        <v>1.9333</v>
+        <v>0.0237</v>
       </c>
       <c r="G64" t="n">
-        <v>415.9975</v>
+        <v>373.0365</v>
       </c>
       <c r="H64" t="n">
-        <v>640.893</v>
+        <v>639.8633</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8373</v>
+        <v>0.9091</v>
       </c>
       <c r="F65" t="n">
-        <v>1.9247</v>
+        <v>0.0269</v>
       </c>
       <c r="G65" t="n">
-        <v>415.4063</v>
+        <v>348.438</v>
       </c>
       <c r="H65" t="n">
-        <v>637.9189</v>
+        <v>638.8185</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8925</v>
+        <v>0.8702</v>
       </c>
       <c r="F66" t="n">
-        <v>1.8897</v>
+        <v>0.0726</v>
       </c>
       <c r="G66" t="n">
-        <v>365.9201</v>
+        <v>399.7172</v>
       </c>
       <c r="H66" t="n">
-        <v>625.7428</v>
+        <v>623.6298</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.8861</v>
       </c>
       <c r="F67" t="n">
-        <v>1.8906</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>357.9847</v>
+        <v>384.1443</v>
       </c>
       <c r="H67" t="n">
-        <v>626.057</v>
+        <v>626.2984</v>
       </c>
     </row>
     <row r="68">
@@ -2590,16 +2590,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8602</v>
+        <v>0.8668</v>
       </c>
       <c r="F68" t="n">
-        <v>1.8989</v>
+        <v>0.0568</v>
       </c>
       <c r="G68" t="n">
-        <v>404.8312</v>
+        <v>400.0594</v>
       </c>
       <c r="H68" t="n">
-        <v>628.9651</v>
+        <v>628.9295</v>
       </c>
     </row>
     <row r="69">
@@ -2622,16 +2622,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9837</v>
+        <v>0.9779</v>
       </c>
       <c r="F69" t="n">
-        <v>1.3136</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>132.2083</v>
+        <v>147.387</v>
       </c>
       <c r="H69" t="n">
-        <v>371.5164</v>
+        <v>374.3704</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9849</v>
+        <v>0.9711</v>
       </c>
       <c r="F70" t="n">
-        <v>1.3061</v>
+        <v>0.6611</v>
       </c>
       <c r="G70" t="n">
-        <v>129.831</v>
+        <v>166.2265</v>
       </c>
       <c r="H70" t="n">
-        <v>367.0531</v>
+        <v>376.9805</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9645</v>
       </c>
       <c r="F71" t="n">
-        <v>1.3322</v>
+        <v>0.6629</v>
       </c>
       <c r="G71" t="n">
-        <v>154.2362</v>
+        <v>179.9446</v>
       </c>
       <c r="H71" t="n">
-        <v>382.3624</v>
+        <v>375.9735</v>
       </c>
     </row>
     <row r="72">
@@ -2714,20 +2714,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9846</v>
+        <v>0.9774</v>
       </c>
       <c r="F72" t="n">
-        <v>1.3188</v>
+        <v>0.6721</v>
       </c>
       <c r="G72" t="n">
-        <v>128.6414</v>
+        <v>146.2967</v>
       </c>
       <c r="H72" t="n">
-        <v>374.5832</v>
+        <v>370.8371</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9534</v>
+        <v>0.9565</v>
       </c>
       <c r="F73" t="n">
-        <v>1.352</v>
+        <v>0.6461</v>
       </c>
       <c r="G73" t="n">
-        <v>217.8375</v>
+        <v>204.2864</v>
       </c>
       <c r="H73" t="n">
-        <v>393.5632</v>
+        <v>385.2313</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9608</v>
+        <v>0.9819</v>
       </c>
       <c r="F74" t="n">
-        <v>1.3441</v>
+        <v>0.6338</v>
       </c>
       <c r="G74" t="n">
-        <v>195.7516</v>
+        <v>142.6342</v>
       </c>
       <c r="H74" t="n">
-        <v>389.167</v>
+        <v>391.8649</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9813</v>
+        <v>0.9426</v>
       </c>
       <c r="F75" t="n">
-        <v>1.4031</v>
+        <v>0.6136</v>
       </c>
       <c r="G75" t="n">
-        <v>142.3639</v>
+        <v>224.4736</v>
       </c>
       <c r="H75" t="n">
-        <v>421.2</v>
+        <v>402.5463</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9813</v>
+        <v>0.9426</v>
       </c>
       <c r="F76" t="n">
-        <v>1.4031</v>
+        <v>0.6136</v>
       </c>
       <c r="G76" t="n">
-        <v>142.3639</v>
+        <v>224.4736</v>
       </c>
       <c r="H76" t="n">
-        <v>421.2</v>
+        <v>402.5463</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8078</v>
+        <v>0.8867</v>
       </c>
       <c r="F77" t="n">
-        <v>1.9481</v>
+        <v>-0.0138</v>
       </c>
       <c r="G77" t="n">
-        <v>436.2959</v>
+        <v>367.5356</v>
       </c>
       <c r="H77" t="n">
-        <v>645.96</v>
+        <v>652.0356</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8083</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>1.9464</v>
+        <v>-0.0163</v>
       </c>
       <c r="G78" t="n">
-        <v>436.2032</v>
+        <v>289.7015</v>
       </c>
       <c r="H78" t="n">
-        <v>645.3871</v>
+        <v>652.8314</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8056</v>
+        <v>0.9448</v>
       </c>
       <c r="F79" t="n">
-        <v>1.9483</v>
+        <v>-0.0219</v>
       </c>
       <c r="G79" t="n">
-        <v>437.057</v>
+        <v>289.1901</v>
       </c>
       <c r="H79" t="n">
-        <v>646.0196</v>
+        <v>654.6281</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8083</v>
+        <v>0.9439</v>
       </c>
       <c r="F80" t="n">
-        <v>1.9464</v>
+        <v>-0.0173</v>
       </c>
       <c r="G80" t="n">
-        <v>436.3704</v>
+        <v>290.2995</v>
       </c>
       <c r="H80" t="n">
-        <v>645.3563</v>
+        <v>653.1636999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8786</v>
+        <v>0.8934</v>
       </c>
       <c r="F81" t="n">
-        <v>1.9031</v>
+        <v>0.028</v>
       </c>
       <c r="G81" t="n">
-        <v>378.13</v>
+        <v>366.2003</v>
       </c>
       <c r="H81" t="n">
-        <v>630.4403</v>
+        <v>638.4571</v>
       </c>
     </row>
     <row r="82">
@@ -3034,20 +3034,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8505</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="F82" t="n">
-        <v>1.9153</v>
+        <v>0.0224</v>
       </c>
       <c r="G82" t="n">
-        <v>407.7278</v>
+        <v>282.9465</v>
       </c>
       <c r="H82" t="n">
-        <v>634.6656</v>
+        <v>640.2872</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9808</v>
+        <v>0.9454</v>
       </c>
       <c r="F83" t="n">
-        <v>1.409</v>
+        <v>0.6077</v>
       </c>
       <c r="G83" t="n">
-        <v>143.341</v>
+        <v>218.4949</v>
       </c>
       <c r="H83" t="n">
-        <v>424.2604</v>
+        <v>405.6305</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9807</v>
+        <v>0.9465</v>
       </c>
       <c r="F84" t="n">
-        <v>1.4082</v>
+        <v>0.6093</v>
       </c>
       <c r="G84" t="n">
-        <v>143.6662</v>
+        <v>216.5274</v>
       </c>
       <c r="H84" t="n">
-        <v>423.838</v>
+        <v>404.7778</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9809</v>
+        <v>0.9403</v>
       </c>
       <c r="F85" t="n">
-        <v>1.4108</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="G85" t="n">
-        <v>143.2959</v>
+        <v>228.1223</v>
       </c>
       <c r="H85" t="n">
-        <v>425.1692</v>
+        <v>406.8415</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9595</v>
       </c>
       <c r="F86" t="n">
-        <v>1.3388</v>
+        <v>0.6534</v>
       </c>
       <c r="G86" t="n">
-        <v>147.9625</v>
+        <v>194.3115</v>
       </c>
       <c r="H86" t="n">
-        <v>386.1339</v>
+        <v>381.2546</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9856</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F87" t="n">
-        <v>1.336</v>
+        <v>0.6684</v>
       </c>
       <c r="G87" t="n">
-        <v>129.8917</v>
+        <v>156.1066</v>
       </c>
       <c r="H87" t="n">
-        <v>384.5359</v>
+        <v>372.8983</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9848</v>
+        <v>0.9777</v>
       </c>
       <c r="F88" t="n">
-        <v>1.3388</v>
+        <v>0.6531</v>
       </c>
       <c r="G88" t="n">
-        <v>133.1557</v>
+        <v>149.92</v>
       </c>
       <c r="H88" t="n">
-        <v>386.1375</v>
+        <v>381.4182</v>
       </c>
     </row>
     <row r="89">
@@ -3262,16 +3262,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9765</v>
+        <v>0.9684</v>
       </c>
       <c r="F89" t="n">
-        <v>1.3469</v>
+        <v>0.651</v>
       </c>
       <c r="G89" t="n">
-        <v>155.3333</v>
+        <v>174.5325</v>
       </c>
       <c r="H89" t="n">
-        <v>390.7489</v>
+        <v>382.5438</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.978</v>
+        <v>0.9657</v>
       </c>
       <c r="F90" t="n">
-        <v>1.322</v>
+        <v>0.7116</v>
       </c>
       <c r="G90" t="n">
-        <v>151.8241</v>
+        <v>180.0638</v>
       </c>
       <c r="H90" t="n">
-        <v>376.4453</v>
+        <v>347.7732</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9859</v>
+        <v>0.9786</v>
       </c>
       <c r="F91" t="n">
-        <v>1.3142</v>
+        <v>0.7089</v>
       </c>
       <c r="G91" t="n">
-        <v>125.7703</v>
+        <v>144.1641</v>
       </c>
       <c r="H91" t="n">
-        <v>371.8546</v>
+        <v>349.4042</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9848</v>
+        <v>0.9777</v>
       </c>
       <c r="F92" t="n">
-        <v>1.3388</v>
+        <v>0.6531</v>
       </c>
       <c r="G92" t="n">
-        <v>133.1557</v>
+        <v>149.92</v>
       </c>
       <c r="H92" t="n">
-        <v>386.1375</v>
+        <v>381.4182</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9859</v>
+        <v>0.9786</v>
       </c>
       <c r="F93" t="n">
-        <v>1.3142</v>
+        <v>0.7089</v>
       </c>
       <c r="G93" t="n">
-        <v>125.7703</v>
+        <v>144.1641</v>
       </c>
       <c r="H93" t="n">
-        <v>371.8546</v>
+        <v>349.4042</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9815</v>
+        <v>0.9404</v>
       </c>
       <c r="F94" t="n">
-        <v>1.4394</v>
+        <v>0.6208</v>
       </c>
       <c r="G94" t="n">
-        <v>147.9455</v>
+        <v>229.1853</v>
       </c>
       <c r="H94" t="n">
-        <v>439.7594</v>
+        <v>398.7601</v>
       </c>
     </row>
     <row r="95">
@@ -3454,16 +3454,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.7975</v>
+        <v>0.7417</v>
       </c>
       <c r="F95" t="n">
-        <v>2.1466</v>
+        <v>-0.0953</v>
       </c>
       <c r="G95" t="n">
-        <v>473.2703</v>
+        <v>487.0662</v>
       </c>
       <c r="H95" t="n">
-        <v>710.3605</v>
+        <v>677.7385</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9818</v>
+        <v>0.9395</v>
       </c>
       <c r="F96" t="n">
-        <v>1.4385</v>
+        <v>0.626</v>
       </c>
       <c r="G96" t="n">
-        <v>147.0156</v>
+        <v>230.4779</v>
       </c>
       <c r="H96" t="n">
-        <v>439.2864</v>
+        <v>396.013</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9819</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F97" t="n">
-        <v>1.4389</v>
+        <v>0.6273</v>
       </c>
       <c r="G97" t="n">
-        <v>146.5793</v>
+        <v>229.6469</v>
       </c>
       <c r="H97" t="n">
-        <v>439.5177</v>
+        <v>395.3574</v>
       </c>
     </row>
     <row r="98">
@@ -3550,16 +3550,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.986</v>
+        <v>0.9847</v>
       </c>
       <c r="F98" t="n">
-        <v>1.3162</v>
+        <v>0.6915</v>
       </c>
       <c r="G98" t="n">
-        <v>130.6339</v>
+        <v>130.7897</v>
       </c>
       <c r="H98" t="n">
-        <v>373.0217</v>
+        <v>359.7153</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9847</v>
+        <v>0.9719</v>
       </c>
       <c r="F99" t="n">
-        <v>1.3148</v>
+        <v>0.6987</v>
       </c>
       <c r="G99" t="n">
-        <v>133.2663</v>
+        <v>166.8183</v>
       </c>
       <c r="H99" t="n">
-        <v>372.1863</v>
+        <v>355.4422</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9856</v>
+        <v>0.969</v>
       </c>
       <c r="F100" t="n">
-        <v>1.32</v>
+        <v>0.7012</v>
       </c>
       <c r="G100" t="n">
-        <v>130.7212</v>
+        <v>173.5619</v>
       </c>
       <c r="H100" t="n">
-        <v>375.2522</v>
+        <v>353.9638</v>
       </c>
     </row>
     <row r="101">
@@ -3646,16 +3646,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9831</v>
       </c>
       <c r="F101" t="n">
-        <v>1.322</v>
+        <v>0.6956</v>
       </c>
       <c r="G101" t="n">
-        <v>129.8188</v>
+        <v>134.4493</v>
       </c>
       <c r="H101" t="n">
-        <v>376.4327</v>
+        <v>357.3129</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9857</v>
+        <v>0.975</v>
       </c>
       <c r="F102" t="n">
-        <v>1.3312</v>
+        <v>0.7004</v>
       </c>
       <c r="G102" t="n">
-        <v>128.3649</v>
+        <v>156.1971</v>
       </c>
       <c r="H102" t="n">
-        <v>381.785</v>
+        <v>354.4555</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9772</v>
       </c>
       <c r="F103" t="n">
-        <v>1.3241</v>
+        <v>0.6943</v>
       </c>
       <c r="G103" t="n">
-        <v>129.5243</v>
+        <v>157.2675</v>
       </c>
       <c r="H103" t="n">
-        <v>377.6631</v>
+        <v>358.0577</v>
       </c>
     </row>
     <row r="104">
@@ -3742,16 +3742,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9861</v>
+        <v>0.9837</v>
       </c>
       <c r="F104" t="n">
-        <v>1.3194</v>
+        <v>0.6919</v>
       </c>
       <c r="G104" t="n">
-        <v>128.943</v>
+        <v>134.7281</v>
       </c>
       <c r="H104" t="n">
-        <v>374.9032</v>
+        <v>359.4657</v>
       </c>
     </row>
     <row r="105">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.98</v>
+        <v>0.9836</v>
       </c>
       <c r="F105" t="n">
-        <v>1.3165</v>
+        <v>0.6965</v>
       </c>
       <c r="G105" t="n">
-        <v>149.144</v>
+        <v>134.8999</v>
       </c>
       <c r="H105" t="n">
-        <v>373.1885</v>
+        <v>356.7518</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9842</v>
+        <v>0.9716</v>
       </c>
       <c r="F106" t="n">
-        <v>1.3108</v>
+        <v>0.6984</v>
       </c>
       <c r="G106" t="n">
-        <v>133.8707</v>
+        <v>166.8358</v>
       </c>
       <c r="H106" t="n">
-        <v>369.8204</v>
+        <v>355.6689</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9852</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="F107" t="n">
-        <v>1.321</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="G107" t="n">
-        <v>130.7216</v>
+        <v>138.9989</v>
       </c>
       <c r="H107" t="n">
-        <v>375.8617</v>
+        <v>359.4206</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9857</v>
+        <v>0.9542</v>
       </c>
       <c r="F108" t="n">
-        <v>1.368</v>
+        <v>0.6521</v>
       </c>
       <c r="G108" t="n">
-        <v>138.0156</v>
+        <v>214.4595</v>
       </c>
       <c r="H108" t="n">
-        <v>402.4533</v>
+        <v>381.9754</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.982</v>
+        <v>0.9678</v>
       </c>
       <c r="F109" t="n">
-        <v>1.3185</v>
+        <v>0.7016</v>
       </c>
       <c r="G109" t="n">
-        <v>146.728</v>
+        <v>180.9832</v>
       </c>
       <c r="H109" t="n">
-        <v>374.4102</v>
+        <v>353.7345</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9848</v>
+        <v>0.9832</v>
       </c>
       <c r="F110" t="n">
-        <v>1.3211</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="G110" t="n">
-        <v>130.263</v>
+        <v>140.0123</v>
       </c>
       <c r="H110" t="n">
-        <v>375.9279</v>
+        <v>361.705</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9825</v>
       </c>
       <c r="F111" t="n">
-        <v>1.3199</v>
+        <v>0.6853</v>
       </c>
       <c r="G111" t="n">
-        <v>153.3862</v>
+        <v>139.9708</v>
       </c>
       <c r="H111" t="n">
-        <v>375.2357</v>
+        <v>363.2774</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9858</v>
+        <v>0.9547</v>
       </c>
       <c r="F112" t="n">
-        <v>1.3631</v>
+        <v>0.6526</v>
       </c>
       <c r="G112" t="n">
-        <v>135.8231</v>
+        <v>213.0762</v>
       </c>
       <c r="H112" t="n">
-        <v>399.7492</v>
+        <v>381.7052</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9822</v>
+        <v>0.9817</v>
       </c>
       <c r="F113" t="n">
-        <v>1.3172</v>
+        <v>0.7008</v>
       </c>
       <c r="G113" t="n">
-        <v>146.349</v>
+        <v>143.4399</v>
       </c>
       <c r="H113" t="n">
-        <v>373.6126</v>
+        <v>354.2339</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9836</v>
+        <v>0.9841</v>
       </c>
       <c r="F114" t="n">
-        <v>1.3176</v>
+        <v>0.6851</v>
       </c>
       <c r="G114" t="n">
-        <v>134.7114</v>
+        <v>138.6549</v>
       </c>
       <c r="H114" t="n">
-        <v>373.8665</v>
+        <v>363.3931</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.978</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="F115" t="n">
-        <v>1.3202</v>
+        <v>0.681</v>
       </c>
       <c r="G115" t="n">
-        <v>154.1862</v>
+        <v>140.6753</v>
       </c>
       <c r="H115" t="n">
-        <v>375.3984</v>
+        <v>365.7539</v>
       </c>
     </row>
     <row r="116">
@@ -4122,20 +4122,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="F116" t="n">
-        <v>1.9345</v>
+        <v>0.0259</v>
       </c>
       <c r="G116" t="n">
-        <v>364.9176</v>
+        <v>435.5092</v>
       </c>
       <c r="H116" t="n">
-        <v>641.3001</v>
+        <v>639.1468</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.8109</v>
       </c>
       <c r="F117" t="n">
-        <v>1.9444</v>
+        <v>0.031</v>
       </c>
       <c r="G117" t="n">
-        <v>371.1572</v>
+        <v>438.1912</v>
       </c>
       <c r="H117" t="n">
-        <v>644.6944999999999</v>
+        <v>637.4530999999999</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.98</v>
+        <v>0.9836</v>
       </c>
       <c r="F118" t="n">
-        <v>1.3165</v>
+        <v>0.6965</v>
       </c>
       <c r="G118" t="n">
-        <v>149.144</v>
+        <v>134.8999</v>
       </c>
       <c r="H118" t="n">
-        <v>373.1885</v>
+        <v>356.7518</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9822</v>
+        <v>0.9817</v>
       </c>
       <c r="F119" t="n">
-        <v>1.3172</v>
+        <v>0.7008</v>
       </c>
       <c r="G119" t="n">
-        <v>146.349</v>
+        <v>143.4399</v>
       </c>
       <c r="H119" t="n">
-        <v>373.6126</v>
+        <v>354.2339</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9363</v>
+        <v>0.9373</v>
       </c>
       <c r="F120" t="n">
-        <v>1.3472</v>
+        <v>0.6725</v>
       </c>
       <c r="G120" t="n">
-        <v>239.9007</v>
+        <v>228.8743</v>
       </c>
       <c r="H120" t="n">
-        <v>390.8713</v>
+        <v>370.5764</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9363</v>
+        <v>0.9373</v>
       </c>
       <c r="F121" t="n">
-        <v>1.3472</v>
+        <v>0.6725</v>
       </c>
       <c r="G121" t="n">
-        <v>239.9007</v>
+        <v>228.8743</v>
       </c>
       <c r="H121" t="n">
-        <v>390.8713</v>
+        <v>370.5764</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9744</v>
+        <v>0.9482</v>
       </c>
       <c r="F122" t="n">
-        <v>1.2869</v>
+        <v>0.6909</v>
       </c>
       <c r="G122" t="n">
-        <v>155.3144</v>
+        <v>210.083</v>
       </c>
       <c r="H122" t="n">
-        <v>355.3553</v>
+        <v>360.0223</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9821</v>
+        <v>0.9817</v>
       </c>
       <c r="F123" t="n">
-        <v>1.3171</v>
+        <v>0.7008</v>
       </c>
       <c r="G123" t="n">
-        <v>146.8122</v>
+        <v>143.4468</v>
       </c>
       <c r="H123" t="n">
-        <v>373.5886</v>
+        <v>354.2178</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9781</v>
+        <v>0.9646</v>
       </c>
       <c r="F124" t="n">
-        <v>1.3301</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G124" t="n">
-        <v>159.782</v>
+        <v>185.2333</v>
       </c>
       <c r="H124" t="n">
-        <v>381.1461</v>
+        <v>359.973</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9812</v>
+        <v>0.9407</v>
       </c>
       <c r="F125" t="n">
-        <v>1.443</v>
+        <v>0.6217</v>
       </c>
       <c r="G125" t="n">
-        <v>148.5925</v>
+        <v>228.5637</v>
       </c>
       <c r="H125" t="n">
-        <v>441.527</v>
+        <v>398.3166</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9801</v>
+        <v>0.9755</v>
       </c>
       <c r="F126" t="n">
-        <v>1.3242</v>
+        <v>0.6985</v>
       </c>
       <c r="G126" t="n">
-        <v>145.2877</v>
+        <v>155.3778</v>
       </c>
       <c r="H126" t="n">
-        <v>377.7509</v>
+        <v>355.5563</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.8449</v>
+        <v>0.8692</v>
       </c>
       <c r="F127" t="n">
-        <v>2.0207</v>
+        <v>-0.0294</v>
       </c>
       <c r="G127" t="n">
-        <v>411.4272</v>
+        <v>388.8515</v>
       </c>
       <c r="H127" t="n">
-        <v>670.217</v>
+        <v>657.0251</v>
       </c>
     </row>
     <row r="128">
@@ -4506,20 +4506,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9728</v>
       </c>
       <c r="F128" t="n">
-        <v>1.3389</v>
+        <v>0.6762</v>
       </c>
       <c r="G128" t="n">
-        <v>130.3922</v>
+        <v>162.5032</v>
       </c>
       <c r="H128" t="n">
-        <v>386.1908</v>
+        <v>368.4724</v>
       </c>
     </row>
     <row r="129">
@@ -4538,20 +4538,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.9858</v>
+        <v>0.968</v>
       </c>
       <c r="F129" t="n">
-        <v>1.3385</v>
+        <v>0.6831</v>
       </c>
       <c r="G129" t="n">
-        <v>129.2235</v>
+        <v>172.8477</v>
       </c>
       <c r="H129" t="n">
-        <v>385.9443</v>
+        <v>364.5405</v>
       </c>
     </row>
     <row r="130">
@@ -4570,20 +4570,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.985</v>
+        <v>0.9673</v>
       </c>
       <c r="F130" t="n">
-        <v>1.3381</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="G130" t="n">
-        <v>129.3455</v>
+        <v>175.6395</v>
       </c>
       <c r="H130" t="n">
-        <v>385.7534</v>
+        <v>369.2311</v>
       </c>
     </row>
     <row r="131">
@@ -4602,20 +4602,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9714</v>
       </c>
       <c r="F131" t="n">
-        <v>1.3436</v>
+        <v>0.6702</v>
       </c>
       <c r="G131" t="n">
-        <v>129.8148</v>
+        <v>164.9685</v>
       </c>
       <c r="H131" t="n">
-        <v>388.8385</v>
+        <v>371.8775</v>
       </c>
     </row>
     <row r="132">
@@ -4634,20 +4634,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.9794</v>
+        <v>0.9787</v>
       </c>
       <c r="F132" t="n">
-        <v>1.333</v>
+        <v>0.697</v>
       </c>
       <c r="G132" t="n">
-        <v>147.1833</v>
+        <v>143.7967</v>
       </c>
       <c r="H132" t="n">
-        <v>382.8252</v>
+        <v>356.4927</v>
       </c>
     </row>
     <row r="133">
@@ -4666,20 +4666,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9789</v>
+        <v>0.9689</v>
       </c>
       <c r="F133" t="n">
-        <v>1.3334</v>
+        <v>0.6901</v>
       </c>
       <c r="G133" t="n">
-        <v>148.5293</v>
+        <v>170.4992</v>
       </c>
       <c r="H133" t="n">
-        <v>383.0337</v>
+        <v>360.5282</v>
       </c>
     </row>
     <row r="134">
@@ -4698,20 +4698,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9784</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="F134" t="n">
-        <v>1.3342</v>
+        <v>0.6891</v>
       </c>
       <c r="G134" t="n">
-        <v>150.0476</v>
+        <v>158.1997</v>
       </c>
       <c r="H134" t="n">
-        <v>383.519</v>
+        <v>361.0623</v>
       </c>
     </row>
     <row r="135">
@@ -4730,20 +4730,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.9858</v>
+        <v>0.9675</v>
       </c>
       <c r="F135" t="n">
-        <v>1.3377</v>
+        <v>0.6906</v>
       </c>
       <c r="G135" t="n">
-        <v>129.0591</v>
+        <v>173.9296</v>
       </c>
       <c r="H135" t="n">
-        <v>385.4843</v>
+        <v>360.2245</v>
       </c>
     </row>
     <row r="136">
@@ -4762,20 +4762,20 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.9857</v>
+        <v>0.9715</v>
       </c>
       <c r="F136" t="n">
-        <v>1.3403</v>
+        <v>0.677</v>
       </c>
       <c r="G136" t="n">
-        <v>128.563</v>
+        <v>164.2245</v>
       </c>
       <c r="H136" t="n">
-        <v>387.002</v>
+        <v>368.0203</v>
       </c>
     </row>
     <row r="137">
@@ -4794,20 +4794,20 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9807</v>
+        <v>0.9709</v>
       </c>
       <c r="F137" t="n">
-        <v>1.3132</v>
+        <v>0.7058</v>
       </c>
       <c r="G137" t="n">
-        <v>141.863</v>
+        <v>166.6711</v>
       </c>
       <c r="H137" t="n">
-        <v>371.2664</v>
+        <v>351.2584</v>
       </c>
     </row>
     <row r="138">
@@ -4826,20 +4826,20 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9759</v>
+        <v>0.9727</v>
       </c>
       <c r="F138" t="n">
-        <v>1.3132</v>
+        <v>0.698</v>
       </c>
       <c r="G138" t="n">
-        <v>156.4093</v>
+        <v>161.42</v>
       </c>
       <c r="H138" t="n">
-        <v>371.2769</v>
+        <v>355.8936</v>
       </c>
     </row>
     <row r="139">
@@ -4858,20 +4858,20 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9805</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="F139" t="n">
-        <v>1.3133</v>
+        <v>0.6999</v>
       </c>
       <c r="G139" t="n">
-        <v>142.4346</v>
+        <v>134.6091</v>
       </c>
       <c r="H139" t="n">
-        <v>371.3006</v>
+        <v>354.7784</v>
       </c>
     </row>
     <row r="140">
@@ -4890,20 +4890,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9852</v>
+        <v>0.9841</v>
       </c>
       <c r="F140" t="n">
-        <v>1.2998</v>
+        <v>0.7007</v>
       </c>
       <c r="G140" t="n">
-        <v>129.0378</v>
+        <v>134.253</v>
       </c>
       <c r="H140" t="n">
-        <v>363.254</v>
+        <v>354.3045</v>
       </c>
     </row>
     <row r="141">
@@ -4922,20 +4922,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9857</v>
+        <v>0.9752</v>
       </c>
       <c r="F141" t="n">
-        <v>1.295</v>
+        <v>0.7037</v>
       </c>
       <c r="G141" t="n">
-        <v>127.3827</v>
+        <v>162.4833</v>
       </c>
       <c r="H141" t="n">
-        <v>360.3129</v>
+        <v>352.4779</v>
       </c>
     </row>
     <row r="142">
@@ -4954,20 +4954,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9759</v>
+        <v>0.9727</v>
       </c>
       <c r="F142" t="n">
-        <v>1.3132</v>
+        <v>0.698</v>
       </c>
       <c r="G142" t="n">
-        <v>156.4093</v>
+        <v>161.42</v>
       </c>
       <c r="H142" t="n">
-        <v>371.2769</v>
+        <v>355.8936</v>
       </c>
     </row>
     <row r="143">
@@ -4986,20 +4986,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9815</v>
       </c>
       <c r="F143" t="n">
-        <v>1.3127</v>
+        <v>0.7066</v>
       </c>
       <c r="G143" t="n">
-        <v>149.5814</v>
+        <v>135.3316</v>
       </c>
       <c r="H143" t="n">
-        <v>370.9851</v>
+        <v>350.799</v>
       </c>
     </row>
     <row r="144">
@@ -5018,20 +5018,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9791</v>
+        <v>0.956</v>
       </c>
       <c r="F144" t="n">
-        <v>1.3087</v>
+        <v>0.7025</v>
       </c>
       <c r="G144" t="n">
-        <v>144.9349</v>
+        <v>199.4172</v>
       </c>
       <c r="H144" t="n">
-        <v>368.6119</v>
+        <v>353.2351</v>
       </c>
     </row>
     <row r="145">
@@ -5050,20 +5050,20 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9857</v>
+        <v>0.9752</v>
       </c>
       <c r="F145" t="n">
-        <v>1.295</v>
+        <v>0.7037</v>
       </c>
       <c r="G145" t="n">
-        <v>127.3827</v>
+        <v>162.4833</v>
       </c>
       <c r="H145" t="n">
-        <v>360.3129</v>
+        <v>352.4779</v>
       </c>
     </row>
     <row r="146">
@@ -5082,20 +5082,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.8467</v>
+        <v>0.8706</v>
       </c>
       <c r="F146" t="n">
-        <v>2.0107</v>
+        <v>-0.0264</v>
       </c>
       <c r="G146" t="n">
-        <v>412.102</v>
+        <v>386.4913</v>
       </c>
       <c r="H146" t="n">
-        <v>666.9450000000001</v>
+        <v>656.0768</v>
       </c>
     </row>
     <row r="147">
@@ -5114,20 +5114,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.8487</v>
+        <v>0.8697</v>
       </c>
       <c r="F147" t="n">
-        <v>2.0157</v>
+        <v>-0.0173</v>
       </c>
       <c r="G147" t="n">
-        <v>409.4122</v>
+        <v>385.7232</v>
       </c>
       <c r="H147" t="n">
-        <v>668.597</v>
+        <v>653.1613</v>
       </c>
     </row>
     <row r="148">
@@ -5146,20 +5146,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.8445</v>
+        <v>0.8717</v>
       </c>
       <c r="F148" t="n">
-        <v>2.0155</v>
+        <v>-0.0126</v>
       </c>
       <c r="G148" t="n">
-        <v>413.5223</v>
+        <v>385.2436</v>
       </c>
       <c r="H148" t="n">
-        <v>668.5302</v>
+        <v>651.6521</v>
       </c>
     </row>
     <row r="149">
@@ -5178,20 +5178,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.8437</v>
+        <v>0.8709</v>
       </c>
       <c r="F149" t="n">
-        <v>2.0176</v>
+        <v>-0.0131</v>
       </c>
       <c r="G149" t="n">
-        <v>413.7097</v>
+        <v>388.9143</v>
       </c>
       <c r="H149" t="n">
-        <v>669.2008</v>
+        <v>651.8228</v>
       </c>
     </row>
     <row r="150">
@@ -5210,20 +5210,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.8711</v>
       </c>
       <c r="F150" t="n">
-        <v>2.0148</v>
+        <v>-0.024</v>
       </c>
       <c r="G150" t="n">
-        <v>410.2758</v>
+        <v>387.1188</v>
       </c>
       <c r="H150" t="n">
-        <v>668.3015</v>
+        <v>655.298</v>
       </c>
     </row>
     <row r="151">
@@ -5242,20 +5242,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.8467</v>
+        <v>0.872</v>
       </c>
       <c r="F151" t="n">
-        <v>2.0179</v>
+        <v>-0.0236</v>
       </c>
       <c r="G151" t="n">
-        <v>409.413</v>
+        <v>386.4452</v>
       </c>
       <c r="H151" t="n">
-        <v>669.2895</v>
+        <v>655.1884</v>
       </c>
     </row>
     <row r="152">
@@ -5274,20 +5274,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.8468</v>
+        <v>0.8714</v>
       </c>
       <c r="F152" t="n">
-        <v>2.0191</v>
+        <v>-0.0263</v>
       </c>
       <c r="G152" t="n">
-        <v>410.5961</v>
+        <v>386.6384</v>
       </c>
       <c r="H152" t="n">
-        <v>669.7025</v>
+        <v>656.0451</v>
       </c>
     </row>
     <row r="153">
@@ -5306,20 +5306,20 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.8435</v>
+        <v>0.8703</v>
       </c>
       <c r="F153" t="n">
-        <v>2.016</v>
+        <v>-0.0264</v>
       </c>
       <c r="G153" t="n">
-        <v>413.7241</v>
+        <v>387.0475</v>
       </c>
       <c r="H153" t="n">
-        <v>668.6964</v>
+        <v>656.085</v>
       </c>
     </row>
     <row r="154">
@@ -5338,20 +5338,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.8468</v>
+        <v>0.8702</v>
       </c>
       <c r="F154" t="n">
-        <v>2.0159</v>
+        <v>-0.023</v>
       </c>
       <c r="G154" t="n">
-        <v>411.9744</v>
+        <v>387.2734</v>
       </c>
       <c r="H154" t="n">
-        <v>668.6466</v>
+        <v>655.002</v>
       </c>
     </row>
     <row r="155">
@@ -5370,20 +5370,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.8822</v>
+        <v>0.8793</v>
       </c>
       <c r="F155" t="n">
-        <v>1.9202</v>
+        <v>0.0311</v>
       </c>
       <c r="G155" t="n">
-        <v>382.0004</v>
+        <v>395.5076</v>
       </c>
       <c r="H155" t="n">
-        <v>636.3786</v>
+        <v>637.4219000000001</v>
       </c>
     </row>
     <row r="156">
@@ -5402,20 +5402,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.844</v>
+        <v>0.8744</v>
       </c>
       <c r="F156" t="n">
-        <v>1.9412</v>
+        <v>0.022</v>
       </c>
       <c r="G156" t="n">
-        <v>415.492</v>
+        <v>399.6576</v>
       </c>
       <c r="H156" t="n">
-        <v>643.5905</v>
+        <v>640.4181</v>
       </c>
     </row>
     <row r="157">
@@ -5434,20 +5434,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.8617</v>
+        <v>0.8452</v>
       </c>
       <c r="F157" t="n">
-        <v>1.9329</v>
+        <v>0.0297</v>
       </c>
       <c r="G157" t="n">
-        <v>399.1334</v>
+        <v>420.2924</v>
       </c>
       <c r="H157" t="n">
-        <v>640.7482</v>
+        <v>637.8963</v>
       </c>
     </row>
     <row r="158">
@@ -5466,20 +5466,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.8575</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="F158" t="n">
-        <v>1.8937</v>
+        <v>0.0852</v>
       </c>
       <c r="G158" t="n">
-        <v>410.2638</v>
+        <v>387.1455</v>
       </c>
       <c r="H158" t="n">
-        <v>627.1333</v>
+        <v>619.3711</v>
       </c>
     </row>
     <row r="159">
@@ -5498,20 +5498,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.9786</v>
+        <v>0.9772</v>
       </c>
       <c r="F159" t="n">
-        <v>1.2978</v>
+        <v>0.6884</v>
       </c>
       <c r="G159" t="n">
-        <v>145.9842</v>
+        <v>148.4598</v>
       </c>
       <c r="H159" t="n">
-        <v>362.0362</v>
+        <v>361.4974</v>
       </c>
     </row>
     <row r="160">
@@ -5530,20 +5530,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.8078</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="F160" t="n">
-        <v>2.0026</v>
+        <v>-0.0399</v>
       </c>
       <c r="G160" t="n">
-        <v>449.6392</v>
+        <v>387.1366</v>
       </c>
       <c r="H160" t="n">
-        <v>664.2560999999999</v>
+        <v>660.378</v>
       </c>
     </row>
     <row r="161">
@@ -5562,20 +5562,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.8455</v>
+        <v>0.8784</v>
       </c>
       <c r="F161" t="n">
-        <v>2.0032</v>
+        <v>-0.0368</v>
       </c>
       <c r="G161" t="n">
-        <v>414.278</v>
+        <v>387.7781</v>
       </c>
       <c r="H161" t="n">
-        <v>664.4628</v>
+        <v>659.3922</v>
       </c>
     </row>
     <row r="162">
@@ -5594,20 +5594,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.978</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="F162" t="n">
-        <v>1.3082</v>
+        <v>0.679</v>
       </c>
       <c r="G162" t="n">
-        <v>148.4737</v>
+        <v>135.7863</v>
       </c>
       <c r="H162" t="n">
-        <v>368.2855</v>
+        <v>366.9162</v>
       </c>
     </row>
     <row r="163">
@@ -5626,20 +5626,20 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9845</v>
+        <v>0.9829</v>
       </c>
       <c r="F163" t="n">
-        <v>1.3233</v>
+        <v>0.6963</v>
       </c>
       <c r="G163" t="n">
-        <v>129.1146</v>
+        <v>135.2759</v>
       </c>
       <c r="H163" t="n">
-        <v>377.2004</v>
+        <v>356.8942</v>
       </c>
     </row>
     <row r="164">
@@ -5658,20 +5658,20 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9852</v>
+        <v>0.9841</v>
       </c>
       <c r="F164" t="n">
-        <v>1.3012</v>
+        <v>0.7006</v>
       </c>
       <c r="G164" t="n">
-        <v>129.1936</v>
+        <v>134.2629</v>
       </c>
       <c r="H164" t="n">
-        <v>364.0913</v>
+        <v>354.3194</v>
       </c>
     </row>
     <row r="165">
@@ -5690,20 +5690,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9812</v>
+        <v>0.9407</v>
       </c>
       <c r="F165" t="n">
-        <v>1.443</v>
+        <v>0.6217</v>
       </c>
       <c r="G165" t="n">
-        <v>148.5925</v>
+        <v>228.5637</v>
       </c>
       <c r="H165" t="n">
-        <v>441.527</v>
+        <v>398.3166</v>
       </c>
     </row>
     <row r="166">
@@ -5726,16 +5726,16 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.7924</v>
+        <v>0.746</v>
       </c>
       <c r="F166" t="n">
-        <v>2.1468</v>
+        <v>-0.1019</v>
       </c>
       <c r="G166" t="n">
-        <v>474.0217</v>
+        <v>484.0932</v>
       </c>
       <c r="H166" t="n">
-        <v>710.4115</v>
+        <v>679.7668</v>
       </c>
     </row>
     <row r="167">
@@ -5754,20 +5754,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9781</v>
+        <v>0.9555</v>
       </c>
       <c r="F167" t="n">
-        <v>1.294</v>
+        <v>0.6996</v>
       </c>
       <c r="G167" t="n">
-        <v>151.5051</v>
+        <v>199.4144</v>
       </c>
       <c r="H167" t="n">
-        <v>359.715</v>
+        <v>354.9492</v>
       </c>
     </row>
     <row r="168">
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.986</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="F168" t="n">
-        <v>1.2783</v>
+        <v>0.7012</v>
       </c>
       <c r="G168" t="n">
-        <v>125.1871</v>
+        <v>126.4969</v>
       </c>
       <c r="H168" t="n">
-        <v>349.9414</v>
+        <v>353.9999</v>
       </c>
     </row>
     <row r="169">
@@ -5818,20 +5818,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9752</v>
+        <v>0.9559</v>
       </c>
       <c r="F169" t="n">
-        <v>1.3423</v>
+        <v>0.6425</v>
       </c>
       <c r="G169" t="n">
-        <v>158.9385</v>
+        <v>199.0488</v>
       </c>
       <c r="H169" t="n">
-        <v>388.1476</v>
+        <v>387.1982</v>
       </c>
     </row>
     <row r="170">
@@ -5850,20 +5850,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9839</v>
+        <v>0.983</v>
       </c>
       <c r="F170" t="n">
-        <v>1.3678</v>
+        <v>0.6419</v>
       </c>
       <c r="G170" t="n">
-        <v>137.8683</v>
+        <v>142.5311</v>
       </c>
       <c r="H170" t="n">
-        <v>402.3166</v>
+        <v>387.5024</v>
       </c>
     </row>
     <row r="171">
@@ -5882,20 +5882,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9772</v>
+        <v>0.98</v>
       </c>
       <c r="F171" t="n">
-        <v>1.3102</v>
+        <v>0.7145</v>
       </c>
       <c r="G171" t="n">
-        <v>156.5498</v>
+        <v>142.6618</v>
       </c>
       <c r="H171" t="n">
-        <v>369.4755</v>
+        <v>346.0434</v>
       </c>
     </row>
     <row r="172">
@@ -5914,20 +5914,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.98</v>
+        <v>0.9827</v>
       </c>
       <c r="F172" t="n">
-        <v>1.2984</v>
+        <v>0.7014</v>
       </c>
       <c r="G172" t="n">
-        <v>143.5005</v>
+        <v>135.8102</v>
       </c>
       <c r="H172" t="n">
-        <v>362.3605</v>
+        <v>353.8495</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E167" t="n">
